--- a/outputs/barcelona_samples_2015_2023_coder1_original-evt.xlsx
+++ b/outputs/barcelona_samples_2015_2023_coder1_original-evt.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="ADD" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="218">
   <si>
     <t xml:space="preserve">Follow-up</t>
   </si>
@@ -788,44 +788,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1083,166 +1087,166 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="1" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="19.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="1" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="19.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>2.11211089874735</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>41.3909679997347</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="2" t="str">
+      <c r="H3" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3909679997347,2.11211089874735","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="6" t="s">
+      <c r="Q3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="V3" s="0" t="str">
+      <c r="V3" s="1" t="str">
         <f aca="false">IF(AND(I3="",K3=""),IF(M3&lt;&gt;"",M3,""),IF(AND(I3&lt;&gt;"",K3=""),I3,IF(AND(I3="",K3&lt;&gt;""),K3,IF(ABS(J3-1)&lt;=ABS(13-L3),I3,K3))))</f>
         <v>1</v>
       </c>
-      <c r="W3" s="0" t="str">
+      <c r="W3" s="1" t="str">
         <f aca="false">IF(AND(O3="",Q3=""),IF(S3&lt;&gt;"",S3,""),IF(AND(O3&lt;&gt;"",Q3=""),O3,IF(AND(O3="",Q3&lt;&gt;""),Q3,IF(ABS(P3-1)&lt;=ABS(13-R3),O3,Q3))))</f>
         <v>0</v>
       </c>
-      <c r="X3" s="8" t="b">
+      <c r="X3" s="9" t="b">
         <f aca="false">IF(OR(V3="",W3=""),"",
   IF(B3="ADD",AND(VALUE(V3)=1,VALUE(W3)=0),
     IF(B3="REMOVE",AND(VALUE(V3)=0,VALUE(W3)=1),
@@ -1254,71 +1258,71 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>2.18031012416</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>41.4581456267453</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H4" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4581456267453,2.18031012416","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" s="7" t="s">
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R4" s="7" t="s">
+      <c r="Q4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="6" t="s">
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="V4" s="0" t="str">
+      <c r="V4" s="1" t="str">
         <f aca="false">IF(AND(I4="",K4=""),IF(M4&lt;&gt;"",M4,""),IF(AND(I4&lt;&gt;"",K4=""),I4,IF(AND(I4="",K4&lt;&gt;""),K4,IF(ABS(J4-1)&lt;=ABS(13-L4),I4,K4))))</f>
         <v>1</v>
       </c>
-      <c r="W4" s="0" t="str">
+      <c r="W4" s="1" t="str">
         <f aca="false">IF(AND(O4="",Q4=""),IF(S4&lt;&gt;"",S4,""),IF(AND(O4&lt;&gt;"",Q4=""),O4,IF(AND(O4="",Q4&lt;&gt;""),Q4,IF(ABS(P4-1)&lt;=ABS(13-R4),O4,Q4))))</f>
         <v>1</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="1" t="n">
         <f aca="false">IF(OR(V4="",W4=""),"",
   IF(B4="ADD",AND(VALUE(V4)=1,VALUE(W4)=0),
     IF(B4="REMOVE",AND(VALUE(V4)=0,VALUE(W4)=1),
@@ -1330,64 +1334,64 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>2.14085269668677</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>41.4134215995416</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4134215995416,2.14085269668677","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="7" t="s">
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="V5" s="0" t="str">
+      <c r="Q5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="V5" s="1" t="str">
         <f aca="false">IF(AND(I5="",K5=""),IF(M5&lt;&gt;"",M5,""),IF(AND(I5&lt;&gt;"",K5=""),I5,IF(AND(I5="",K5&lt;&gt;""),K5,IF(ABS(J5-1)&lt;=ABS(13-L5),I5,K5))))</f>
         <v>1</v>
       </c>
-      <c r="W5" s="0" t="str">
+      <c r="W5" s="1" t="str">
         <f aca="false">IF(AND(O5="",Q5=""),IF(S5&lt;&gt;"",S5,""),IF(AND(O5&lt;&gt;"",Q5=""),O5,IF(AND(O5="",Q5&lt;&gt;""),Q5,IF(ABS(P5-1)&lt;=ABS(13-R5),O5,Q5))))</f>
         <v>0</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="1" t="n">
         <f aca="false">IF(OR(V5="",W5=""),"",
   IF(B5="ADD",AND(VALUE(V5)=1,VALUE(W5)=0),
     IF(B5="REMOVE",AND(VALUE(V5)=0,VALUE(W5)=1),
@@ -1399,68 +1403,68 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>2.20113165987653</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>41.4262832087554</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="2" t="str">
+      <c r="H6" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4262832087554,2.20113165987653","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="7" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="V6" s="0" t="str">
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="V6" s="1" t="str">
         <f aca="false">IF(AND(I6="",K6=""),IF(M6&lt;&gt;"",M6,""),IF(AND(I6&lt;&gt;"",K6=""),I6,IF(AND(I6="",K6&lt;&gt;""),K6,IF(ABS(J6-1)&lt;=ABS(13-L6),I6,K6))))</f>
         <v>1</v>
       </c>
-      <c r="W6" s="0" t="str">
+      <c r="W6" s="1" t="str">
         <f aca="false">IF(AND(O6="",Q6=""),IF(S6&lt;&gt;"",S6,""),IF(AND(O6&lt;&gt;"",Q6=""),O6,IF(AND(O6="",Q6&lt;&gt;""),Q6,IF(ABS(P6-1)&lt;=ABS(13-R6),O6,Q6))))</f>
         <v>0</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="1" t="n">
         <f aca="false">IF(OR(V6="",W6=""),"",
   IF(B6="ADD",AND(VALUE(V6)=1,VALUE(W6)=0),
     IF(B6="REMOVE",AND(VALUE(V6)=0,VALUE(W6)=1),
@@ -1472,71 +1476,71 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>2.2001190522901</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>41.4260327049088</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="2" t="str">
+      <c r="H7" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4260327049088,2.2001190522901","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R7" s="7" t="s">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="6" t="s">
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="V7" s="0" t="str">
+      <c r="V7" s="1" t="str">
         <f aca="false">IF(AND(I7="",K7=""),IF(M7&lt;&gt;"",M7,""),IF(AND(I7&lt;&gt;"",K7=""),I7,IF(AND(I7="",K7&lt;&gt;""),K7,IF(ABS(J7-1)&lt;=ABS(13-L7),I7,K7))))</f>
         <v>1</v>
       </c>
-      <c r="W7" s="0" t="str">
+      <c r="W7" s="1" t="str">
         <f aca="false">IF(AND(O7="",Q7=""),IF(S7&lt;&gt;"",S7,""),IF(AND(O7&lt;&gt;"",Q7=""),O7,IF(AND(O7="",Q7&lt;&gt;""),Q7,IF(ABS(P7-1)&lt;=ABS(13-R7),O7,Q7))))</f>
         <v>0</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="1" t="n">
         <f aca="false">IF(OR(V7="",W7=""),"",
   IF(B7="ADD",AND(VALUE(V7)=1,VALUE(W7)=0),
     IF(B7="REMOVE",AND(VALUE(V7)=0,VALUE(W7)=1),
@@ -1548,60 +1552,60 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>2.13402755812853</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>41.3881854073843</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="2" t="str">
+      <c r="H8" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3881854073843,2.13402755812853","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="M8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="7" t="s">
+      <c r="M8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="7" t="s">
+      <c r="Q8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="V8" s="0" t="str">
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="V8" s="1" t="str">
         <f aca="false">IF(AND(I9="",K9=""),IF(M8&lt;&gt;"",M8,""),IF(AND(I9&lt;&gt;"",K9=""),I9,IF(AND(I9="",K9&lt;&gt;""),K9,IF(ABS(J9-1)&lt;=ABS(13-L9),I9,K9))))</f>
         <v>1</v>
       </c>
-      <c r="W8" s="0" t="str">
+      <c r="W8" s="1" t="str">
         <f aca="false">IF(AND(O8="",Q8=""),IF(S8&lt;&gt;"",S8,""),IF(AND(O8&lt;&gt;"",Q8=""),O8,IF(AND(O8="",Q8&lt;&gt;""),Q8,IF(ABS(P8-1)&lt;=ABS(13-R8),O8,Q8))))</f>
         <v>0</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="1" t="n">
         <f aca="false">IF(OR(V8="",W8=""),"",
   IF(B8="ADD",AND(VALUE(V8)=1,VALUE(W8)=0),
     IF(B8="REMOVE",AND(VALUE(V8)=0,VALUE(W8)=1),
@@ -1613,71 +1617,71 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>2.19881673887713</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>41.4168121764961</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="2" t="str">
+      <c r="H9" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4168121764961,2.19881673887713","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="6" t="s">
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="V9" s="0" t="str">
+      <c r="V9" s="1" t="str">
         <f aca="false">IF(AND(I9="",K9=""),IF(M9&lt;&gt;"",M9,""),IF(AND(I9&lt;&gt;"",K9=""),I9,IF(AND(I9="",K9&lt;&gt;""),K9,IF(ABS(J9-1)&lt;=ABS(13-L9),I9,K9))))</f>
         <v>1</v>
       </c>
-      <c r="W9" s="0" t="str">
+      <c r="W9" s="1" t="str">
         <f aca="false">IF(AND(O9="",Q9=""),IF(S9&lt;&gt;"",S9,""),IF(AND(O9&lt;&gt;"",Q9=""),O9,IF(AND(O9="",Q9&lt;&gt;""),Q9,IF(ABS(P9-1)&lt;=ABS(13-R9),O9,Q9))))</f>
         <v>1</v>
       </c>
-      <c r="X9" s="8" t="n">
+      <c r="X9" s="1" t="n">
         <f aca="false">IF(OR(V9="",W9=""),"",
   IF(B9="ADD",AND(VALUE(V9)=1,VALUE(W9)=0),
     IF(B9="REMOVE",AND(VALUE(V9)=0,VALUE(W9)=1),
@@ -1689,59 +1693,59 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>2.17205102853822</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>41.414975730964</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="2" t="str">
+      <c r="H10" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414975730964,2.17205102853822","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R10" s="7" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="6" t="s">
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="X10" s="8" t="str">
+      <c r="X10" s="1" t="str">
         <f aca="false">IF(OR(V10="",W10=""),"",
   IF(B10="ADD",AND(VALUE(V10)=1,VALUE(W10)=0),
     IF(B10="REMOVE",AND(VALUE(V10)=0,VALUE(W10)=1),
@@ -1753,68 +1757,68 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>2.17461017557639</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>41.4168653577514</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="2" t="str">
+      <c r="H11" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4168653577514,2.17461017557639","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R11" s="7" t="s">
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="V11" s="0" t="str">
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="V11" s="1" t="str">
         <f aca="false">IF(AND(I11="",K11=""),IF(M11&lt;&gt;"",M11,""),IF(AND(I11&lt;&gt;"",K11=""),I11,IF(AND(I11="",K11&lt;&gt;""),K11,IF(ABS(J11-1)&lt;=ABS(13-L11),I11,K11))))</f>
         <v>1</v>
       </c>
-      <c r="W11" s="0" t="str">
+      <c r="W11" s="1" t="str">
         <f aca="false">IF(AND(O11="",Q11=""),IF(S11&lt;&gt;"",S11,""),IF(AND(O11&lt;&gt;"",Q11=""),O11,IF(AND(O11="",Q11&lt;&gt;""),Q11,IF(ABS(P11-1)&lt;=ABS(13-R11),O11,Q11))))</f>
         <v>0</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="1" t="n">
         <f aca="false">IF(OR(V11="",W11=""),"",
   IF(B11="ADD",AND(VALUE(V11)=1,VALUE(W11)=0),
     IF(B11="REMOVE",AND(VALUE(V11)=0,VALUE(W11)=1),
@@ -1826,64 +1830,64 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>2.20794256929774</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>41.4202454258576</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="2" t="str">
+      <c r="H12" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4202454258576,2.20794256929774","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R12" s="7" t="s">
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="V12" s="0" t="str">
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="V12" s="1" t="str">
         <f aca="false">IF(AND(I12="",K12=""),IF(M12&lt;&gt;"",M12,""),IF(AND(I12&lt;&gt;"",K12=""),I12,IF(AND(I12="",K12&lt;&gt;""),K12,IF(ABS(J12-1)&lt;=ABS(13-L12),I12,K12))))</f>
         <v>1</v>
       </c>
-      <c r="W12" s="0" t="str">
+      <c r="W12" s="1" t="str">
         <f aca="false">IF(AND(O12="",Q12=""),IF(S12&lt;&gt;"",S12,""),IF(AND(O12&lt;&gt;"",Q12=""),O12,IF(AND(O12="",Q12&lt;&gt;""),Q12,IF(ABS(P12-1)&lt;=ABS(13-R12),O12,Q12))))</f>
         <v>1</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="1" t="n">
         <f aca="false">IF(OR(V12="",W12=""),"",
   IF(B12="ADD",AND(VALUE(V12)=1,VALUE(W12)=0),
     IF(B12="REMOVE",AND(VALUE(V12)=0,VALUE(W12)=1),
@@ -1895,68 +1899,68 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>2.16098092184219</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>41.4121092794043</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="2" t="str">
+      <c r="H13" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4121092794043,2.16098092184219","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="V13" s="0" t="str">
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="V13" s="1" t="str">
         <f aca="false">IF(AND(I13="",K13=""),IF(M13&lt;&gt;"",M13,""),IF(AND(I13&lt;&gt;"",K13=""),I13,IF(AND(I13="",K13&lt;&gt;""),K13,IF(ABS(J13-1)&lt;=ABS(13-L13),I13,K13))))</f>
         <v>1</v>
       </c>
-      <c r="W13" s="0" t="str">
+      <c r="W13" s="1" t="str">
         <f aca="false">IF(AND(O13="",Q13=""),IF(S13&lt;&gt;"",S13,""),IF(AND(O13&lt;&gt;"",Q13=""),O13,IF(AND(O13="",Q13&lt;&gt;""),Q13,IF(ABS(P13-1)&lt;=ABS(13-R13),O13,Q13))))</f>
         <v>0</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="1" t="n">
         <f aca="false">IF(OR(V13="",W13=""),"",
   IF(B13="ADD",AND(VALUE(V13)=1,VALUE(W13)=0),
     IF(B13="REMOVE",AND(VALUE(V13)=0,VALUE(W13)=1),
@@ -1968,67 +1972,67 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>2.16175831110785</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>41.4125465819168</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="2" t="str">
+      <c r="H14" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4125465819168,2.16175831110785","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="7" t="s">
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="6" t="s">
+      <c r="Q14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="V14" s="0" t="str">
+      <c r="V14" s="1" t="str">
         <f aca="false">IF(AND(I14="",K14=""),IF(M14&lt;&gt;"",M14,""),IF(AND(I14&lt;&gt;"",K14=""),I14,IF(AND(I14="",K14&lt;&gt;""),K14,IF(ABS(J14-1)&lt;=ABS(13-L14),I14,K14))))</f>
         <v>1</v>
       </c>
-      <c r="W14" s="0" t="str">
+      <c r="W14" s="1" t="str">
         <f aca="false">IF(AND(O14="",Q14=""),IF(S14&lt;&gt;"",S14,""),IF(AND(O14&lt;&gt;"",Q14=""),O14,IF(AND(O14="",Q14&lt;&gt;""),Q14,IF(ABS(P14-1)&lt;=ABS(13-R14),O14,Q14))))</f>
         <v>0</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="1" t="n">
         <f aca="false">IF(OR(V14="",W14=""),"",
   IF(B14="ADD",AND(VALUE(V14)=1,VALUE(W14)=0),
     IF(B14="REMOVE",AND(VALUE(V14)=0,VALUE(W14)=1),
@@ -2040,71 +2044,71 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>2.20077256303846</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>41.3945206907087</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H15" s="2" t="str">
+      <c r="H15" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3945206907087,2.20077256303846","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="I15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="7" t="s">
+      <c r="K15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="6" t="s">
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="V15" s="0" t="str">
+      <c r="V15" s="1" t="str">
         <f aca="false">IF(AND(I15="",K15=""),IF(M15&lt;&gt;"",M15,""),IF(AND(I15&lt;&gt;"",K15=""),I15,IF(AND(I15="",K15&lt;&gt;""),K15,IF(ABS(J15-1)&lt;=ABS(13-L15),I15,K15))))</f>
         <v>1</v>
       </c>
-      <c r="W15" s="0" t="str">
+      <c r="W15" s="1" t="str">
         <f aca="false">IF(AND(O15="",Q15=""),IF(S15&lt;&gt;"",S15,""),IF(AND(O15&lt;&gt;"",Q15=""),O15,IF(AND(O15="",Q15&lt;&gt;""),Q15,IF(ABS(P15-1)&lt;=ABS(13-R15),O15,Q15))))</f>
         <v>0</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="1" t="n">
         <f aca="false">IF(OR(V15="",W15=""),"",
   IF(B15="ADD",AND(VALUE(V15)=1,VALUE(W15)=0),
     IF(B15="REMOVE",AND(VALUE(V15)=0,VALUE(W15)=1),
@@ -2116,68 +2120,68 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>2.20100922656311</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>41.394718915396</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="2" t="str">
+      <c r="H16" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.394718915396,2.20100922656311","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="7" t="s">
+      <c r="K16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="V16" s="0" t="str">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="V16" s="1" t="str">
         <f aca="false">IF(AND(I16="",K16=""),IF(M16&lt;&gt;"",M16,""),IF(AND(I16&lt;&gt;"",K16=""),I16,IF(AND(I16="",K16&lt;&gt;""),K16,IF(ABS(J16-1)&lt;=ABS(13-L16),I16,K16))))</f>
         <v>1</v>
       </c>
-      <c r="W16" s="0" t="str">
+      <c r="W16" s="1" t="str">
         <f aca="false">IF(AND(O16="",Q16=""),IF(S16&lt;&gt;"",S16,""),IF(AND(O16&lt;&gt;"",Q16=""),O16,IF(AND(O16="",Q16&lt;&gt;""),Q16,IF(ABS(P16-1)&lt;=ABS(13-R16),O16,Q16))))</f>
         <v>0</v>
       </c>
-      <c r="X16" s="8" t="n">
+      <c r="X16" s="1" t="n">
         <f aca="false">IF(OR(V16="",W16=""),"",
   IF(B16="ADD",AND(VALUE(V16)=1,VALUE(W16)=0),
     IF(B16="REMOVE",AND(VALUE(V16)=0,VALUE(W16)=1),
@@ -2189,64 +2193,64 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>2.14512744406006</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>41.3761865969803</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="2" t="str">
+      <c r="H17" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3761865969803,2.14512744406006","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="7" t="s">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="7" t="s">
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R17" s="7" t="s">
+      <c r="Q17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="V17" s="0" t="str">
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="V17" s="1" t="str">
         <f aca="false">IF(AND(I17="",K17=""),IF(M17&lt;&gt;"",M17,""),IF(AND(I17&lt;&gt;"",K17=""),I17,IF(AND(I17="",K17&lt;&gt;""),K17,IF(ABS(J17-1)&lt;=ABS(13-L17),I17,K17))))</f>
         <v>1</v>
       </c>
-      <c r="W17" s="0" t="str">
+      <c r="W17" s="1" t="str">
         <f aca="false">IF(AND(O17="",Q17=""),IF(S17&lt;&gt;"",S17,""),IF(AND(O17&lt;&gt;"",Q17=""),O17,IF(AND(O17="",Q17&lt;&gt;""),Q17,IF(ABS(P17-1)&lt;=ABS(13-R17),O17,Q17))))</f>
         <v>0</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="X17" s="1" t="n">
         <f aca="false">IF(OR(V17="",W17=""),"",
   IF(B17="ADD",AND(VALUE(V17)=1,VALUE(W17)=0),
     IF(B17="REMOVE",AND(VALUE(V17)=0,VALUE(W17)=1),
@@ -2258,59 +2262,63 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>2.14788692420496</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>41.3759905523005</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="2" t="str">
+      <c r="H18" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3759905523005,2.14788692420496","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" s="7" t="s">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="6" t="s">
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="V18" s="0" t="str">
+      <c r="V18" s="1" t="str">
         <f aca="false">IF(AND(I18="",K18=""),IF(M18&lt;&gt;"",M18,""),IF(AND(I18&lt;&gt;"",K18=""),I18,IF(AND(I18="",K18&lt;&gt;""),K18,IF(ABS(J18-1)&lt;=ABS(13-L18),I18,K18))))</f>
         <v>0</v>
       </c>
-      <c r="W18" s="0" t="str">
+      <c r="W18" s="1" t="str">
         <f aca="false">IF(AND(O18="",Q18=""),IF(S18&lt;&gt;"",S18,""),IF(AND(O18&lt;&gt;"",Q18=""),O18,IF(AND(O18="",Q18&lt;&gt;""),Q18,IF(ABS(P18-1)&lt;=ABS(13-R18),O18,Q18))))</f>
-        <v/>
-      </c>
-      <c r="X18" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1" t="b">
         <f aca="false">IF(OR(V18="",W18=""),"",
   IF(B18="ADD",AND(VALUE(V18)=1,VALUE(W18)=0),
     IF(B18="REMOVE",AND(VALUE(V18)=0,VALUE(W18)=1),
@@ -2318,72 +2326,72 @@
     )
   )
 )</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>2.18284748138898</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <v>41.4055753756871</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="2" t="str">
+      <c r="H19" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4055753756871,2.18284748138898","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="I19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="K19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R19" s="7" t="s">
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="V19" s="0" t="str">
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="V19" s="1" t="str">
         <f aca="false">IF(AND(I19="",K19=""),IF(M19&lt;&gt;"",M19,""),IF(AND(I19&lt;&gt;"",K19=""),I19,IF(AND(I19="",K19&lt;&gt;""),K19,IF(ABS(J19-1)&lt;=ABS(13-L19),I19,K19))))</f>
         <v>1</v>
       </c>
-      <c r="W19" s="0" t="str">
+      <c r="W19" s="1" t="str">
         <f aca="false">IF(AND(O19="",Q19=""),IF(S19&lt;&gt;"",S19,""),IF(AND(O19&lt;&gt;"",Q19=""),O19,IF(AND(O19="",Q19&lt;&gt;""),Q19,IF(ABS(P19-1)&lt;=ABS(13-R19),O19,Q19))))</f>
         <v>0</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="1" t="n">
         <f aca="false">IF(OR(V19="",W19=""),"",
   IF(B19="ADD",AND(VALUE(V19)=1,VALUE(W19)=0),
     IF(B19="REMOVE",AND(VALUE(V19)=0,VALUE(W19)=1),
@@ -2395,68 +2403,68 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>2.18283205987351</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>41.4031168392834</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="2" t="str">
+      <c r="H20" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4031168392834,2.18283205987351","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="7" t="s">
+      <c r="I20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="7" t="s">
+      <c r="K20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R20" s="7" t="s">
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="V20" s="0" t="str">
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="V20" s="1" t="str">
         <f aca="false">IF(AND(I20="",K20=""),IF(M20&lt;&gt;"",M20,""),IF(AND(I20&lt;&gt;"",K20=""),I20,IF(AND(I20="",K20&lt;&gt;""),K20,IF(ABS(J20-1)&lt;=ABS(13-L20),I20,K20))))</f>
         <v>1</v>
       </c>
-      <c r="W20" s="0" t="str">
+      <c r="W20" s="1" t="str">
         <f aca="false">IF(AND(O20="",Q20=""),IF(S20&lt;&gt;"",S20,""),IF(AND(O20&lt;&gt;"",Q20=""),O20,IF(AND(O20="",Q20&lt;&gt;""),Q20,IF(ABS(P20-1)&lt;=ABS(13-R20),O20,Q20))))</f>
         <v>0</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="1" t="n">
         <f aca="false">IF(OR(V20="",W20=""),"",
   IF(B20="ADD",AND(VALUE(V20)=1,VALUE(W20)=0),
     IF(B20="REMOVE",AND(VALUE(V20)=0,VALUE(W20)=1),
@@ -2468,63 +2476,63 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>2.17585558557915</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>41.4287555466715</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H21" s="2" t="str">
+      <c r="H21" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4287555466715,2.17585558557915","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R21" s="7" t="s">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R21" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="6" t="s">
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="V21" s="0" t="str">
+      <c r="V21" s="1" t="str">
         <f aca="false">IF(AND(I21="",K21=""),IF(M21&lt;&gt;"",M21,""),IF(AND(I21&lt;&gt;"",K21=""),I21,IF(AND(I21="",K21&lt;&gt;""),K21,IF(ABS(J21-1)&lt;=ABS(13-L21),I21,K21))))</f>
         <v>0</v>
       </c>
-      <c r="W21" s="0" t="str">
+      <c r="W21" s="1" t="str">
         <f aca="false">IF(AND(O21="",Q21=""),IF(S21&lt;&gt;"",S21,""),IF(AND(O21&lt;&gt;"",Q21=""),O21,IF(AND(O21="",Q21&lt;&gt;""),Q21,IF(ABS(P21-1)&lt;=ABS(13-R21),O21,Q21))))</f>
         <v>0</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="X21" s="1" t="n">
         <f aca="false">IF(OR(V21="",W21=""),"",
   IF(B21="ADD",AND(VALUE(V21)=1,VALUE(W21)=0),
     IF(B21="REMOVE",AND(VALUE(V21)=0,VALUE(W21)=1),
@@ -2536,68 +2544,68 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <v>2.19083141351904</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <v>41.4409954760919</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H22" s="2" t="str">
+      <c r="H22" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4409954760919,2.19083141351904","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J22" s="7" t="s">
+      <c r="I22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="7" t="s">
+      <c r="K22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P22" s="7" t="s">
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R22" s="7" t="s">
+      <c r="Q22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="V22" s="0" t="str">
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="V22" s="1" t="str">
         <f aca="false">IF(AND(I22="",K22=""),IF(M22&lt;&gt;"",M22,""),IF(AND(I22&lt;&gt;"",K22=""),I22,IF(AND(I22="",K22&lt;&gt;""),K22,IF(ABS(J22-1)&lt;=ABS(13-L22),I22,K22))))</f>
         <v>1</v>
       </c>
-      <c r="W22" s="0" t="str">
+      <c r="W22" s="1" t="str">
         <f aca="false">IF(AND(O22="",Q22=""),IF(S22&lt;&gt;"",S22,""),IF(AND(O22&lt;&gt;"",Q22=""),O22,IF(AND(O22="",Q22&lt;&gt;""),Q22,IF(ABS(P22-1)&lt;=ABS(13-R22),O22,Q22))))</f>
         <v>1</v>
       </c>
-      <c r="X22" s="8" t="n">
+      <c r="X22" s="1" t="n">
         <f aca="false">IF(OR(V22="",W22=""),"",
   IF(B22="ADD",AND(VALUE(V22)=1,VALUE(W22)=0),
     IF(B22="REMOVE",AND(VALUE(V22)=0,VALUE(W22)=1),
@@ -2609,68 +2617,68 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>2.15155610489397</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="1" t="n">
         <v>41.4003124653889</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H23" s="2" t="str">
+      <c r="H23" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4003124653889,2.15155610489397","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" s="7" t="s">
+      <c r="I23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="7" t="s">
+      <c r="K23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P23" s="7" t="s">
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="V23" s="0" t="str">
+      <c r="Q23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="V23" s="1" t="str">
         <f aca="false">IF(AND(I23="",K23=""),IF(M23&lt;&gt;"",M23,""),IF(AND(I23&lt;&gt;"",K23=""),I23,IF(AND(I23="",K23&lt;&gt;""),K23,IF(ABS(J23-1)&lt;=ABS(13-L23),I23,K23))))</f>
         <v>1</v>
       </c>
-      <c r="W23" s="0" t="str">
+      <c r="W23" s="1" t="str">
         <f aca="false">IF(AND(O23="",Q23=""),IF(S23&lt;&gt;"",S23,""),IF(AND(O23&lt;&gt;"",Q23=""),O23,IF(AND(O23="",Q23&lt;&gt;""),Q23,IF(ABS(P23-1)&lt;=ABS(13-R23),O23,Q23))))</f>
         <v>0</v>
       </c>
-      <c r="X23" s="8" t="n">
+      <c r="X23" s="1" t="n">
         <f aca="false">IF(OR(V23="",W23=""),"",
   IF(B23="ADD",AND(VALUE(V23)=1,VALUE(W23)=0),
     IF(B23="REMOVE",AND(VALUE(V23)=0,VALUE(W23)=1),
@@ -2682,68 +2690,68 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>2.1512519597158</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <v>41.400537545303</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="2" t="str">
+      <c r="H24" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.400537545303,2.1512519597158","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7" t="s">
+      <c r="I24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="K24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P24" s="7" t="s">
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="V24" s="0" t="str">
+      <c r="Q24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="V24" s="1" t="str">
         <f aca="false">IF(AND(I24="",K24=""),IF(M24&lt;&gt;"",M24,""),IF(AND(I24&lt;&gt;"",K24=""),I24,IF(AND(I24="",K24&lt;&gt;""),K24,IF(ABS(J24-1)&lt;=ABS(13-L24),I24,K24))))</f>
         <v>1</v>
       </c>
-      <c r="W24" s="0" t="str">
+      <c r="W24" s="1" t="str">
         <f aca="false">IF(AND(O24="",Q24=""),IF(S24&lt;&gt;"",S24,""),IF(AND(O24&lt;&gt;"",Q24=""),O24,IF(AND(O24="",Q24&lt;&gt;""),Q24,IF(ABS(P24-1)&lt;=ABS(13-R24),O24,Q24))))</f>
         <v>0</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="1" t="n">
         <f aca="false">IF(OR(V24="",W24=""),"",
   IF(B24="ADD",AND(VALUE(V24)=1,VALUE(W24)=0),
     IF(B24="REMOVE",AND(VALUE(V24)=0,VALUE(W24)=1),
@@ -2755,64 +2763,64 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>2.13625700853396</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <v>41.3859805190525</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="G25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H25" s="2" t="str">
+      <c r="H25" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3859805190525,2.13625700853396","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P25" s="7" t="s">
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="V25" s="0" t="str">
+      <c r="Q25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="V25" s="1" t="str">
         <f aca="false">IF(AND(I25="",K25=""),IF(M25&lt;&gt;"",M25,""),IF(AND(I25&lt;&gt;"",K25=""),I25,IF(AND(I25="",K25&lt;&gt;""),K25,IF(ABS(J25-1)&lt;=ABS(13-L25),I25,K25))))</f>
         <v>1</v>
       </c>
-      <c r="W25" s="0" t="str">
+      <c r="W25" s="1" t="str">
         <f aca="false">IF(AND(O25="",Q25=""),IF(S25&lt;&gt;"",S25,""),IF(AND(O25&lt;&gt;"",Q25=""),O25,IF(AND(O25="",Q25&lt;&gt;""),Q25,IF(ABS(P25-1)&lt;=ABS(13-R25),O25,Q25))))</f>
         <v>0</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="1" t="n">
         <f aca="false">IF(OR(V25="",W25=""),"",
   IF(B25="ADD",AND(VALUE(V25)=1,VALUE(W25)=0),
     IF(B25="REMOVE",AND(VALUE(V25)=0,VALUE(W25)=1),
@@ -2824,64 +2832,64 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <v>2.13854147438959</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <v>41.385461059572</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="2" t="str">
+      <c r="H26" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.385461059572,2.13854147438959","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P26" s="7" t="s">
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="V26" s="0" t="str">
+      <c r="Q26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="V26" s="1" t="str">
         <f aca="false">IF(AND(I26="",K26=""),IF(M26&lt;&gt;"",M26,""),IF(AND(I26&lt;&gt;"",K26=""),I26,IF(AND(I26="",K26&lt;&gt;""),K26,IF(ABS(J26-1)&lt;=ABS(13-L26),I26,K26))))</f>
         <v>1</v>
       </c>
-      <c r="W26" s="0" t="str">
+      <c r="W26" s="1" t="str">
         <f aca="false">IF(AND(O26="",Q26=""),IF(S26&lt;&gt;"",S26,""),IF(AND(O26&lt;&gt;"",Q26=""),O26,IF(AND(O26="",Q26&lt;&gt;""),Q26,IF(ABS(P26-1)&lt;=ABS(13-R26),O26,Q26))))</f>
         <v>0</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="1" t="n">
         <f aca="false">IF(OR(V26="",W26=""),"",
   IF(B26="ADD",AND(VALUE(V26)=1,VALUE(W26)=0),
     IF(B26="REMOVE",AND(VALUE(V26)=0,VALUE(W26)=1),
@@ -2893,71 +2901,71 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>2.18533799661021</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <v>41.3903749358271</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="G27" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H27" s="2" t="str">
+      <c r="H27" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3903749358271,2.18533799661021","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J27" s="7" t="s">
+      <c r="I27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="7" t="s">
+      <c r="K27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R27" s="7" t="s">
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R27" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="6" t="s">
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="V27" s="0" t="str">
+      <c r="V27" s="1" t="str">
         <f aca="false">IF(AND(I27="",K27=""),IF(M27&lt;&gt;"",M27,""),IF(AND(I27&lt;&gt;"",K27=""),I27,IF(AND(I27="",K27&lt;&gt;""),K27,IF(ABS(J27-1)&lt;=ABS(13-L27),I27,K27))))</f>
         <v>1</v>
       </c>
-      <c r="W27" s="0" t="str">
+      <c r="W27" s="1" t="str">
         <f aca="false">IF(AND(O27="",Q27=""),IF(S27&lt;&gt;"",S27,""),IF(AND(O27&lt;&gt;"",Q27=""),O27,IF(AND(O27="",Q27&lt;&gt;""),Q27,IF(ABS(P27-1)&lt;=ABS(13-R27),O27,Q27))))</f>
         <v>0</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="X27" s="1" t="n">
         <f aca="false">IF(OR(V27="",W27=""),"",
   IF(B27="ADD",AND(VALUE(V27)=1,VALUE(W27)=0),
     IF(B27="REMOVE",AND(VALUE(V27)=0,VALUE(W27)=1),
@@ -2969,71 +2977,71 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <v>2.18642991571189</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="1" t="n">
         <v>41.3911878676426</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="G28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="2" t="str">
+      <c r="H28" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3911878676426,2.18642991571189","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J28" s="7" t="s">
+      <c r="I28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="7" t="s">
+      <c r="K28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="6" t="s">
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="V28" s="0" t="str">
+      <c r="V28" s="1" t="str">
         <f aca="false">IF(AND(I28="",K28=""),IF(M28&lt;&gt;"",M28,""),IF(AND(I28&lt;&gt;"",K28=""),I28,IF(AND(I28="",K28&lt;&gt;""),K28,IF(ABS(J28-1)&lt;=ABS(13-L28),I28,K28))))</f>
         <v>1</v>
       </c>
-      <c r="W28" s="0" t="str">
+      <c r="W28" s="1" t="str">
         <f aca="false">IF(AND(O28="",Q28=""),IF(S28&lt;&gt;"",S28,""),IF(AND(O28&lt;&gt;"",Q28=""),O28,IF(AND(O28="",Q28&lt;&gt;""),Q28,IF(ABS(P28-1)&lt;=ABS(13-R28),O28,Q28))))</f>
         <v>0</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="X28" s="1" t="n">
         <f aca="false">IF(OR(V28="",W28=""),"",
   IF(B28="ADD",AND(VALUE(V28)=1,VALUE(W28)=0),
     IF(B28="REMOVE",AND(VALUE(V28)=0,VALUE(W28)=1),
@@ -3045,59 +3053,59 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <v>2.15897555292765</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="1" t="n">
         <v>41.3826431790481</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="G29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="2" t="str">
+      <c r="H29" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3826431790481,2.15897555292765","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="7" t="s">
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="6" t="s">
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="X29" s="8" t="str">
+      <c r="X29" s="1" t="str">
         <f aca="false">IF(OR(V29="",W29=""),"",
   IF(B29="ADD",AND(VALUE(V29)=1,VALUE(W29)=0),
     IF(B29="REMOVE",AND(VALUE(V29)=0,VALUE(W29)=1),
@@ -3109,68 +3117,68 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="1" t="n">
         <v>2.1537501547691</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="1" t="n">
         <v>41.3981332109611</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="G30" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H30" s="2" t="str">
+      <c r="H30" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3981332109611,2.1537501547691","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J30" s="7" t="s">
+      <c r="I30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="7" t="s">
+      <c r="K30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P30" s="7" t="s">
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R30" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="V30" s="0" t="str">
+      <c r="Q30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="V30" s="1" t="str">
         <f aca="false">IF(AND(I30="",K30=""),IF(M30&lt;&gt;"",M30,""),IF(AND(I30&lt;&gt;"",K30=""),I30,IF(AND(I30="",K30&lt;&gt;""),K30,IF(ABS(J30-1)&lt;=ABS(13-L30),I30,K30))))</f>
         <v>1</v>
       </c>
-      <c r="W30" s="0" t="str">
+      <c r="W30" s="1" t="str">
         <f aca="false">IF(AND(O30="",Q30=""),IF(S30&lt;&gt;"",S30,""),IF(AND(O30&lt;&gt;"",Q30=""),O30,IF(AND(O30="",Q30&lt;&gt;""),Q30,IF(ABS(P30-1)&lt;=ABS(13-R30),O30,Q30))))</f>
         <v>0</v>
       </c>
-      <c r="X30" s="8" t="n">
+      <c r="X30" s="1" t="n">
         <f aca="false">IF(OR(V30="",W30=""),"",
   IF(B30="ADD",AND(VALUE(V30)=1,VALUE(W30)=0),
     IF(B30="REMOVE",AND(VALUE(V30)=0,VALUE(W30)=1),
@@ -3182,68 +3190,68 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="1" t="n">
         <v>2.12400952913739</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="1" t="n">
         <v>41.3756644128399</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="G31" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H31" s="2" t="str">
+      <c r="H31" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3756644128399,2.12400952913739","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="I31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L31" s="7" t="s">
+      <c r="K31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P31" s="7" t="s">
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R31" s="7" t="s">
+      <c r="Q31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R31" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="V31" s="0" t="str">
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="V31" s="1" t="str">
         <f aca="false">IF(AND(I31="",K31=""),IF(M31&lt;&gt;"",M31,""),IF(AND(I31&lt;&gt;"",K31=""),I31,IF(AND(I31="",K31&lt;&gt;""),K31,IF(ABS(J31-1)&lt;=ABS(13-L31),I31,K31))))</f>
         <v>1</v>
       </c>
-      <c r="W31" s="0" t="str">
+      <c r="W31" s="1" t="str">
         <f aca="false">IF(AND(O31="",Q31=""),IF(S31&lt;&gt;"",S31,""),IF(AND(O31&lt;&gt;"",Q31=""),O31,IF(AND(O31="",Q31&lt;&gt;""),Q31,IF(ABS(P31-1)&lt;=ABS(13-R31),O31,Q31))))</f>
         <v>0</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="1" t="n">
         <f aca="false">IF(OR(V31="",W31=""),"",
   IF(B31="ADD",AND(VALUE(V31)=1,VALUE(W31)=0),
     IF(B31="REMOVE",AND(VALUE(V31)=0,VALUE(W31)=1),
@@ -3255,67 +3263,67 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="0" t="s">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="1" t="n">
         <v>2.17976081270432</v>
       </c>
-      <c r="F32" s="0" t="n">
+      <c r="F32" s="1" t="n">
         <v>41.4118804921772</v>
       </c>
-      <c r="G32" s="0" t="s">
+      <c r="G32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="2" t="str">
+      <c r="H32" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4118804921772,2.17976081270432","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L32" s="7" t="s">
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P32" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R32" s="7" t="s">
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R32" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="6" t="s">
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="V32" s="0" t="str">
+      <c r="V32" s="1" t="str">
         <f aca="false">IF(AND(I32="",K32=""),IF(M32&lt;&gt;"",M32,""),IF(AND(I32&lt;&gt;"",K32=""),I32,IF(AND(I32="",K32&lt;&gt;""),K32,IF(ABS(J32-1)&lt;=ABS(13-L32),I32,K32))))</f>
         <v>1</v>
       </c>
-      <c r="W32" s="0" t="str">
+      <c r="W32" s="1" t="str">
         <f aca="false">IF(AND(O32="",Q32=""),IF(S32&lt;&gt;"",S32,""),IF(AND(O32&lt;&gt;"",Q32=""),O32,IF(AND(O32="",Q32&lt;&gt;""),Q32,IF(ABS(P32-1)&lt;=ABS(13-R32),O32,Q32))))</f>
         <v>0</v>
       </c>
-      <c r="X32" s="8" t="n">
+      <c r="X32" s="1" t="n">
         <f aca="false">IF(OR(V32="",W32=""),"",
   IF(B32="ADD",AND(VALUE(V32)=1,VALUE(W32)=0),
     IF(B32="REMOVE",AND(VALUE(V32)=0,VALUE(W32)=1),
@@ -3327,59 +3335,59 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="0" t="s">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <v>2.180890772398</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="1" t="n">
         <v>41.4127447371871</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H33" s="2" t="str">
+      <c r="H33" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4127447371871,2.180890772398","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" s="7" t="s">
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="6" t="s">
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="X33" s="8" t="str">
+      <c r="X33" s="1" t="str">
         <f aca="false">IF(OR(V33="",W33=""),"",
   IF(B33="ADD",AND(VALUE(V33)=1,VALUE(W33)=0),
     IF(B33="REMOVE",AND(VALUE(V33)=0,VALUE(W33)=1),
@@ -3391,64 +3399,64 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <v>2.13774430876668</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <v>41.3845333231462</v>
       </c>
-      <c r="G34" s="0" t="s">
+      <c r="G34" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H34" s="2" t="str">
+      <c r="H34" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3845333231462,2.13774430876668","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P34" s="7" t="s">
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R34" s="7" t="s">
+      <c r="Q34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="V34" s="0" t="str">
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="V34" s="1" t="str">
         <f aca="false">IF(AND(I34="",K34=""),IF(M34&lt;&gt;"",M34,""),IF(AND(I34&lt;&gt;"",K34=""),I34,IF(AND(I34="",K34&lt;&gt;""),K34,IF(ABS(J34-1)&lt;=ABS(13-L34),I34,K34))))</f>
         <v>1</v>
       </c>
-      <c r="W34" s="0" t="str">
+      <c r="W34" s="1" t="str">
         <f aca="false">IF(AND(O34="",Q34=""),IF(S34&lt;&gt;"",S34,""),IF(AND(O34&lt;&gt;"",Q34=""),O34,IF(AND(O34="",Q34&lt;&gt;""),Q34,IF(ABS(P34-1)&lt;=ABS(13-R34),O34,Q34))))</f>
         <v>0</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="1" t="n">
         <f aca="false">IF(OR(V34="",W34=""),"",
   IF(B34="ADD",AND(VALUE(V34)=1,VALUE(W34)=0),
     IF(B34="REMOVE",AND(VALUE(V34)=0,VALUE(W34)=1),
@@ -3460,67 +3468,67 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="0" t="s">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <v>2.1379907548408</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="1" t="n">
         <v>41.3851587554757</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="G35" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H35" s="2" t="str">
+      <c r="H35" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3851587554757,2.1379907548408","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N35" s="7" t="s">
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="O35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P35" s="7" t="s">
+      <c r="O35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P35" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q35" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="6" t="s">
+      <c r="Q35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="V35" s="0" t="str">
+      <c r="V35" s="1" t="str">
         <f aca="false">IF(AND(I35="",K35=""),IF(M35&lt;&gt;"",M35,""),IF(AND(I35&lt;&gt;"",K35=""),I35,IF(AND(I35="",K35&lt;&gt;""),K35,IF(ABS(J35-1)&lt;=ABS(13-L35),I35,K35))))</f>
         <v>1</v>
       </c>
-      <c r="W35" s="0" t="str">
+      <c r="W35" s="1" t="str">
         <f aca="false">IF(AND(O35="",Q35=""),IF(S35&lt;&gt;"",S35,""),IF(AND(O35&lt;&gt;"",Q35=""),O35,IF(AND(O35="",Q35&lt;&gt;""),Q35,IF(ABS(P35-1)&lt;=ABS(13-R35),O35,Q35))))</f>
         <v>1</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="1" t="n">
         <f aca="false">IF(OR(V35="",W35=""),"",
   IF(B35="ADD",AND(VALUE(V35)=1,VALUE(W35)=0),
     IF(B35="REMOVE",AND(VALUE(V35)=0,VALUE(W35)=1),
@@ -3532,64 +3540,64 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <v>2.13925763528919</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="1" t="n">
         <v>41.3600114226598</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H36" s="2" t="str">
+      <c r="H36" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3600114226598,2.13925763528919","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P36" s="7" t="s">
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R36" s="7" t="s">
+      <c r="Q36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R36" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="V36" s="0" t="str">
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="V36" s="1" t="str">
         <f aca="false">IF(AND(I36="",K36=""),IF(M36&lt;&gt;"",M36,""),IF(AND(I36&lt;&gt;"",K36=""),I36,IF(AND(I36="",K36&lt;&gt;""),K36,IF(ABS(J36-1)&lt;=ABS(13-L36),I36,K36))))</f>
         <v>1</v>
       </c>
-      <c r="W36" s="0" t="str">
+      <c r="W36" s="1" t="str">
         <f aca="false">IF(AND(O36="",Q36=""),IF(S36&lt;&gt;"",S36,""),IF(AND(O36&lt;&gt;"",Q36=""),O36,IF(AND(O36="",Q36&lt;&gt;""),Q36,IF(ABS(P36-1)&lt;=ABS(13-R36),O36,Q36))))</f>
         <v>0</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="1" t="n">
         <f aca="false">IF(OR(V36="",W36=""),"",
   IF(B36="ADD",AND(VALUE(V36)=1,VALUE(W36)=0),
     IF(B36="REMOVE",AND(VALUE(V36)=0,VALUE(W36)=1),
@@ -3601,64 +3609,64 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <v>2.14988483545966</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="1" t="n">
         <v>41.3826401063928</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H37" s="2" t="str">
+      <c r="H37" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3826401063928,2.14988483545966","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L37" s="7" t="s">
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P37" s="7" t="s">
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R37" s="7" t="s">
+      <c r="Q37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R37" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="V37" s="0" t="str">
+      <c r="S37" s="8"/>
+      <c r="T37" s="8"/>
+      <c r="V37" s="1" t="str">
         <f aca="false">IF(AND(I37="",K37=""),IF(M37&lt;&gt;"",M37,""),IF(AND(I37&lt;&gt;"",K37=""),I37,IF(AND(I37="",K37&lt;&gt;""),K37,IF(ABS(J37-1)&lt;=ABS(13-L37),I37,K37))))</f>
         <v>1</v>
       </c>
-      <c r="W37" s="0" t="str">
+      <c r="W37" s="1" t="str">
         <f aca="false">IF(AND(O37="",Q37=""),IF(S37&lt;&gt;"",S37,""),IF(AND(O37&lt;&gt;"",Q37=""),O37,IF(AND(O37="",Q37&lt;&gt;""),Q37,IF(ABS(P37-1)&lt;=ABS(13-R37),O37,Q37))))</f>
         <v>0</v>
       </c>
-      <c r="X37" s="8" t="n">
+      <c r="X37" s="1" t="n">
         <f aca="false">IF(OR(V37="",W37=""),"",
   IF(B37="ADD",AND(VALUE(V37)=1,VALUE(W37)=0),
     IF(B37="REMOVE",AND(VALUE(V37)=0,VALUE(W37)=1),
@@ -3670,68 +3678,68 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <v>2.15108663385983</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="1" t="n">
         <v>41.3817275823745</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H38" s="2" t="str">
+      <c r="H38" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3817275823745,2.15108663385983","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J38" s="7" t="s">
+      <c r="I38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L38" s="7" t="s">
+      <c r="K38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P38" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R38" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="V38" s="0" t="str">
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S38" s="8"/>
+      <c r="T38" s="8"/>
+      <c r="V38" s="1" t="str">
         <f aca="false">IF(AND(I38="",K38=""),IF(M38&lt;&gt;"",M38,""),IF(AND(I38&lt;&gt;"",K38=""),I38,IF(AND(I38="",K38&lt;&gt;""),K38,IF(ABS(J38-1)&lt;=ABS(13-L38),I38,K38))))</f>
         <v>1</v>
       </c>
-      <c r="W38" s="0" t="str">
+      <c r="W38" s="1" t="str">
         <f aca="false">IF(AND(O38="",Q38=""),IF(S38&lt;&gt;"",S38,""),IF(AND(O38&lt;&gt;"",Q38=""),O38,IF(AND(O38="",Q38&lt;&gt;""),Q38,IF(ABS(P38-1)&lt;=ABS(13-R38),O38,Q38))))</f>
         <v>0</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="1" t="n">
         <f aca="false">IF(OR(V38="",W38=""),"",
   IF(B38="ADD",AND(VALUE(V38)=1,VALUE(W38)=0),
     IF(B38="REMOVE",AND(VALUE(V38)=0,VALUE(W38)=1),
@@ -3743,55 +3751,55 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <v>2.15362165090984</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="1" t="n">
         <v>41.3781971000936</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H39" s="2" t="str">
+      <c r="H39" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3781971000936,2.15362165090984","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L39" s="7" t="s">
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L39" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P39" s="7" t="s">
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="6" t="s">
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="X39" s="8" t="str">
+      <c r="X39" s="1" t="str">
         <f aca="false">IF(OR(V39="",W39=""),"",
   IF(B39="ADD",AND(VALUE(V39)=1,VALUE(W39)=0),
     IF(B39="REMOVE",AND(VALUE(V39)=0,VALUE(W39)=1),
@@ -3803,71 +3811,71 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <v>2.14763895462665</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <v>41.3826129597012</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H40" s="2" t="str">
+      <c r="H40" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3826129597012,2.14763895462665","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J40" s="7" t="s">
+      <c r="I40" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L40" s="7" t="s">
+      <c r="K40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P40" s="7" t="s">
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="6" t="s">
+      <c r="Q40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R40" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="V40" s="0" t="str">
+      <c r="V40" s="1" t="str">
         <f aca="false">IF(AND(I40="",K40=""),IF(M40&lt;&gt;"",M40,""),IF(AND(I40&lt;&gt;"",K40=""),I40,IF(AND(I40="",K40&lt;&gt;""),K40,IF(ABS(J40-1)&lt;=ABS(13-L40),I40,K40))))</f>
         <v>1</v>
       </c>
-      <c r="W40" s="0" t="str">
+      <c r="W40" s="1" t="str">
         <f aca="false">IF(AND(O40="",Q40=""),IF(S40&lt;&gt;"",S40,""),IF(AND(O40&lt;&gt;"",Q40=""),O40,IF(AND(O40="",Q40&lt;&gt;""),Q40,IF(ABS(P40-1)&lt;=ABS(13-R40),O40,Q40))))</f>
         <v>0</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="1" t="n">
         <f aca="false">IF(OR(V40="",W40=""),"",
   IF(B40="ADD",AND(VALUE(V40)=1,VALUE(W40)=0),
     IF(B40="REMOVE",AND(VALUE(V40)=0,VALUE(W40)=1),
@@ -3879,64 +3887,64 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <v>2.14820775338395</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="1" t="n">
         <v>41.3830424246768</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="G41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H41" s="2" t="str">
+      <c r="H41" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3830424246768,2.14820775338395","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L41" s="7" t="s">
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P41" s="7" t="s">
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P41" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R41" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="V41" s="0" t="str">
+      <c r="Q41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="V41" s="1" t="str">
         <f aca="false">IF(AND(I41="",K41=""),IF(M41&lt;&gt;"",M41,""),IF(AND(I41&lt;&gt;"",K41=""),I41,IF(AND(I41="",K41&lt;&gt;""),K41,IF(ABS(J41-1)&lt;=ABS(13-L41),I41,K41))))</f>
         <v>0</v>
       </c>
-      <c r="W41" s="0" t="str">
+      <c r="W41" s="1" t="str">
         <f aca="false">IF(AND(O41="",Q41=""),IF(S41&lt;&gt;"",S41,""),IF(AND(O41&lt;&gt;"",Q41=""),O41,IF(AND(O41="",Q41&lt;&gt;""),Q41,IF(ABS(P41-1)&lt;=ABS(13-R41),O41,Q41))))</f>
         <v>0</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="1" t="n">
         <f aca="false">IF(OR(V41="",W41=""),"",
   IF(B41="ADD",AND(VALUE(V41)=1,VALUE(W41)=0),
     IF(B41="REMOVE",AND(VALUE(V41)=0,VALUE(W41)=1),
@@ -3948,7 +3956,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="10" t="n">
         <f aca="false">COUNTIF(X:X,1)/34</f>
         <v>0.794117647058824</v>
       </c>
@@ -3975,169 +3983,169 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:X8"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="1" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="1" style="1" width="13.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>2.10400617396064</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>41.3849403989724</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="2" t="str">
+      <c r="H3" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3849403989724,2.10400617396064","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="7" t="s">
+      <c r="Q3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="6" t="s">
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="V3" s="0" t="str">
+      <c r="V3" s="1" t="str">
         <f aca="false">IF(AND(I3="",K3=""),IF(M3&lt;&gt;"",M3,""),IF(AND(I3&lt;&gt;"",K3=""),I3,IF(AND(I3="",K3&lt;&gt;""),K3,IF(ABS(J3-1)&lt;=ABS(13-L3),I3,K3))))</f>
         <v>0</v>
       </c>
-      <c r="W3" s="0" t="str">
+      <c r="W3" s="1" t="str">
         <f aca="false">IF(AND(O3="",Q3=""),IF(S3&lt;&gt;"",S3,""),IF(AND(O3&lt;&gt;"",Q3=""),O3,IF(AND(O3="",Q3&lt;&gt;""),Q3,IF(ABS(P3-1)&lt;=ABS(13-R3),O3,Q3))))</f>
         <v>0</v>
       </c>
-      <c r="X3" s="8" t="b">
+      <c r="X3" s="9" t="b">
         <f aca="false">IF(OR(V3="",W3=""),"",
   IF(B3="ADD",AND(VALUE(V3)=1,VALUE(W3)=0),
     IF(B3="REMOVE",AND(VALUE(V3)=0,VALUE(W3)=1),
@@ -4149,64 +4157,64 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>2.17979187635586</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>41.4325734990105</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H4" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4325734990105,2.17979187635586","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="7" t="s">
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" s="7" t="s">
+      <c r="O4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="V4" s="0" t="str">
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="V4" s="1" t="str">
         <f aca="false">IF(AND(I4="",K4=""),IF(M4&lt;&gt;"",M4,""),IF(AND(I4&lt;&gt;"",K4=""),I4,IF(AND(I4="",K4&lt;&gt;""),K4,IF(ABS(J4-1)&lt;=ABS(13-L4),I4,K4))))</f>
         <v>0</v>
       </c>
-      <c r="W4" s="0" t="str">
+      <c r="W4" s="1" t="str">
         <f aca="false">IF(AND(O4="",Q4=""),IF(S4&lt;&gt;"",S4,""),IF(AND(O4&lt;&gt;"",Q4=""),O4,IF(AND(O4="",Q4&lt;&gt;""),Q4,IF(ABS(P4-1)&lt;=ABS(13-R4),O4,Q4))))</f>
         <v>0</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="1" t="n">
         <f aca="false">IF(OR(V4="",W4=""),"",
   IF(B4="ADD",AND(VALUE(V4)=1,VALUE(W4)=0),
     IF(B4="REMOVE",AND(VALUE(V4)=0,VALUE(W4)=1),
@@ -4218,68 +4226,68 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>2.17443553665477</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>41.4302401188698</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4302401188698,2.17443553665477","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" s="7" t="s">
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="V5" s="0" t="str">
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="V5" s="1" t="str">
         <f aca="false">IF(AND(I5="",K5=""),IF(M5&lt;&gt;"",M5,""),IF(AND(I5&lt;&gt;"",K5=""),I5,IF(AND(I5="",K5&lt;&gt;""),K5,IF(ABS(J5-1)&lt;=ABS(13-L5),I5,K5))))</f>
         <v>0</v>
       </c>
-      <c r="W5" s="0" t="str">
+      <c r="W5" s="1" t="str">
         <f aca="false">IF(AND(O5="",Q5=""),IF(S5&lt;&gt;"",S5,""),IF(AND(O5&lt;&gt;"",Q5=""),O5,IF(AND(O5="",Q5&lt;&gt;""),Q5,IF(ABS(P5-1)&lt;=ABS(13-R5),O5,Q5))))</f>
         <v>0</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="1" t="n">
         <f aca="false">IF(OR(V5="",W5=""),"",
   IF(B5="ADD",AND(VALUE(V5)=1,VALUE(W5)=0),
     IF(B5="REMOVE",AND(VALUE(V5)=0,VALUE(W5)=1),
@@ -4291,64 +4299,64 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>2.15681272246318</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>41.3843400360326</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="2" t="str">
+      <c r="H6" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3843400360326,2.15681272246318","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="7" t="s">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="7" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R6" s="7" t="s">
+      <c r="Q6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="V6" s="0" t="str">
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="V6" s="1" t="str">
         <f aca="false">IF(AND(I6="",K6=""),IF(M6&lt;&gt;"",M6,""),IF(AND(I6&lt;&gt;"",K6=""),I6,IF(AND(I6="",K6&lt;&gt;""),K6,IF(ABS(J6-1)&lt;=ABS(13-L6),I6,K6))))</f>
         <v>0</v>
       </c>
-      <c r="W6" s="0" t="str">
+      <c r="W6" s="1" t="str">
         <f aca="false">IF(AND(O6="",Q6=""),IF(S6&lt;&gt;"",S6,""),IF(AND(O6&lt;&gt;"",Q6=""),O6,IF(AND(O6="",Q6&lt;&gt;""),Q6,IF(ABS(P6-1)&lt;=ABS(13-R6),O6,Q6))))</f>
         <v>1</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="1" t="n">
         <f aca="false">IF(OR(V6="",W6=""),"",
   IF(B6="ADD",AND(VALUE(V6)=1,VALUE(W6)=0),
     IF(B6="REMOVE",AND(VALUE(V6)=0,VALUE(W6)=1),
@@ -4360,67 +4368,67 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>2.15726201275132</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>41.3832798659396</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H7" s="2" t="str">
+      <c r="H7" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3832798659396,2.15726201275132","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="7" t="s">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="6" t="s">
+      <c r="Q7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V7" s="0" t="str">
+      <c r="V7" s="1" t="str">
         <f aca="false">IF(AND(I7="",K7=""),IF(M7&lt;&gt;"",M7,""),IF(AND(I7&lt;&gt;"",K7=""),I7,IF(AND(I7="",K7&lt;&gt;""),K7,IF(ABS(J7-1)&lt;=ABS(13-L7),I7,K7))))</f>
         <v>1</v>
       </c>
-      <c r="W7" s="0" t="str">
+      <c r="W7" s="1" t="str">
         <f aca="false">IF(AND(O7="",Q7=""),IF(S7&lt;&gt;"",S7,""),IF(AND(O7&lt;&gt;"",Q7=""),O7,IF(AND(O7="",Q7&lt;&gt;""),Q7,IF(ABS(P7-1)&lt;=ABS(13-R7),O7,Q7))))</f>
         <v>1</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="1" t="n">
         <f aca="false">IF(OR(V7="",W7=""),"",
   IF(B7="ADD",AND(VALUE(V7)=1,VALUE(W7)=0),
     IF(B7="REMOVE",AND(VALUE(V7)=0,VALUE(W7)=1),
@@ -4432,64 +4440,64 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>2.13049998390271</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>41.3753699099384</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H8" s="2" t="str">
+      <c r="H8" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3753699099384,2.13049998390271","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="7" t="s">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="7" t="s">
+      <c r="Q8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="V8" s="0" t="str">
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="V8" s="1" t="str">
         <f aca="false">IF(AND(I8="",K8=""),IF(M8&lt;&gt;"",M8,""),IF(AND(I8&lt;&gt;"",K8=""),I8,IF(AND(I8="",K8&lt;&gt;""),K8,IF(ABS(J8-1)&lt;=ABS(13-L8),I8,K8))))</f>
         <v>0</v>
       </c>
-      <c r="W8" s="0" t="str">
+      <c r="W8" s="1" t="str">
         <f aca="false">IF(AND(O8="",Q8=""),IF(S8&lt;&gt;"",S8,""),IF(AND(O8&lt;&gt;"",Q8=""),O8,IF(AND(O8="",Q8&lt;&gt;""),Q8,IF(ABS(P8-1)&lt;=ABS(13-R8),O8,Q8))))</f>
         <v>0</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="1" t="n">
         <f aca="false">IF(OR(V8="",W8=""),"",
   IF(B8="ADD",AND(VALUE(V8)=1,VALUE(W8)=0),
     IF(B8="REMOVE",AND(VALUE(V8)=0,VALUE(W8)=1),
@@ -4522,166 +4530,166 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:X52"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="1" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="1" style="1" width="13.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>2.10966944882359</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>41.3931098000992</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H3" s="2" t="str">
+      <c r="H3" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3931098000992,2.10966944882359","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="7" t="s">
+      <c r="Q3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="V3" s="0" t="str">
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="V3" s="1" t="str">
         <f aca="false">IF(AND(I3="",K3=""),IF(M3&lt;&gt;"",M3,""),IF(AND(I3&lt;&gt;"",K3=""),I3,IF(AND(I3="",K3&lt;&gt;""),K3,IF(ABS(J3-1)&lt;=ABS(13-L3),I3,K3))))</f>
         <v>0</v>
       </c>
-      <c r="W3" s="0" t="str">
+      <c r="W3" s="1" t="str">
         <f aca="false">IF(AND(O3="",Q3=""),IF(S3&lt;&gt;"",S3,""),IF(AND(O3&lt;&gt;"",Q3=""),O3,IF(AND(O3="",Q3&lt;&gt;""),Q3,IF(ABS(P3-1)&lt;=ABS(13-R3),O3,Q3))))</f>
         <v>0</v>
       </c>
-      <c r="X3" s="8" t="b">
+      <c r="X3" s="9" t="b">
         <f aca="false">IF(OR(V3="",W3=""),"",
   IF(B3="ADD",AND(VALUE(V3)=1,VALUE(W3)=0),
     IF(B3="REMOVE",AND(VALUE(V3)=0,VALUE(W3)=1),
@@ -4693,68 +4701,68 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>2.17168660935981</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>41.426710550311</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H4" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.426710550311,2.17168660935981","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="7" t="s">
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" s="7" t="s">
+      <c r="Q4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="V4" s="0" t="str">
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="V4" s="1" t="str">
         <f aca="false">IF(AND(I4="",K4=""),IF(M4&lt;&gt;"",M4,""),IF(AND(I4&lt;&gt;"",K4=""),I4,IF(AND(I4="",K4&lt;&gt;""),K4,IF(ABS(J4-1)&lt;=ABS(13-L4),I4,K4))))</f>
         <v>0</v>
       </c>
-      <c r="W4" s="0" t="str">
+      <c r="W4" s="1" t="str">
         <f aca="false">IF(AND(O4="",Q4=""),IF(S4&lt;&gt;"",S4,""),IF(AND(O4&lt;&gt;"",Q4=""),O4,IF(AND(O4="",Q4&lt;&gt;""),Q4,IF(ABS(P4-1)&lt;=ABS(13-R4),O4,Q4))))</f>
         <v>0</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="1" t="n">
         <f aca="false">IF(OR(V4="",W4=""),"",
   IF(B4="ADD",AND(VALUE(V4)=1,VALUE(W4)=0),
     IF(B4="REMOVE",AND(VALUE(V4)=0,VALUE(W4)=1),
@@ -4766,60 +4774,60 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>2.18391622731384</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>41.4552112160084</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4552112160084,2.18391622731384","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" s="7" t="s">
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="V5" s="0" t="str">
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="V5" s="1" t="str">
         <f aca="false">IF(AND(I5="",K5=""),IF(M5&lt;&gt;"",M5,""),IF(AND(I5&lt;&gt;"",K5=""),I5,IF(AND(I5="",K5&lt;&gt;""),K5,IF(ABS(J5-1)&lt;=ABS(13-L5),I5,K5))))</f>
         <v>0</v>
       </c>
-      <c r="W5" s="0" t="str">
+      <c r="W5" s="1" t="str">
         <f aca="false">IF(AND(O5="",Q5=""),IF(S5&lt;&gt;"",S5,""),IF(AND(O5&lt;&gt;"",Q5=""),O5,IF(AND(O5="",Q5&lt;&gt;""),Q5,IF(ABS(P5-1)&lt;=ABS(13-R5),O5,Q5))))</f>
         <v>0</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="1" t="n">
         <f aca="false">IF(OR(V5="",W5=""),"",
   IF(B5="ADD",AND(VALUE(V5)=1,VALUE(W5)=0),
     IF(B5="REMOVE",AND(VALUE(V5)=0,VALUE(W5)=1),
@@ -4831,60 +4839,60 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>2.14041149568948</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>41.4133726186721</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H6" s="2" t="str">
+      <c r="H6" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4133726186721,2.14041149568948","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="7" t="s">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="V6" s="0" t="str">
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="V6" s="1" t="str">
         <f aca="false">IF(AND(I6="",K6=""),IF(M6&lt;&gt;"",M6,""),IF(AND(I6&lt;&gt;"",K6=""),I6,IF(AND(I6="",K6&lt;&gt;""),K6,IF(ABS(J6-1)&lt;=ABS(13-L6),I6,K6))))</f>
         <v>1</v>
       </c>
-      <c r="W6" s="0" t="str">
+      <c r="W6" s="1" t="str">
         <f aca="false">IF(AND(O6="",Q6=""),IF(S6&lt;&gt;"",S6,""),IF(AND(O6&lt;&gt;"",Q6=""),O6,IF(AND(O6="",Q6&lt;&gt;""),Q6,IF(ABS(P6-1)&lt;=ABS(13-R6),O6,Q6))))</f>
         <v>0</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="1" t="n">
         <f aca="false">IF(OR(V6="",W6=""),"",
   IF(B6="ADD",AND(VALUE(V6)=1,VALUE(W6)=0),
     IF(B6="REMOVE",AND(VALUE(V6)=0,VALUE(W6)=1),
@@ -4896,60 +4904,60 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>2.20826181490227</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>41.4219065425505</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H7" s="2" t="str">
+      <c r="H7" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4219065425505,2.20826181490227","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="7" t="s">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="V7" s="0" t="str">
+      <c r="V7" s="1" t="str">
         <f aca="false">IF(AND(I7="",K7=""),IF(M7&lt;&gt;"",M7,""),IF(AND(I7&lt;&gt;"",K7=""),I7,IF(AND(I7="",K7&lt;&gt;""),K7,IF(ABS(J7-1)&lt;=ABS(13-L7),I7,K7))))</f>
         <v>0</v>
       </c>
-      <c r="W7" s="0" t="str">
+      <c r="W7" s="1" t="str">
         <f aca="false">IF(AND(O7="",Q7=""),IF(S7&lt;&gt;"",S7,""),IF(AND(O7&lt;&gt;"",Q7=""),O7,IF(AND(O7="",Q7&lt;&gt;""),Q7,IF(ABS(P7-1)&lt;=ABS(13-R7),O7,Q7))))</f>
         <v>0</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="1" t="n">
         <f aca="false">IF(OR(V7="",W7=""),"",
   IF(B7="ADD",AND(VALUE(V7)=1,VALUE(W7)=0),
     IF(B7="REMOVE",AND(VALUE(V7)=0,VALUE(W7)=1),
@@ -4961,64 +4969,64 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>2.20484681868868</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>41.4258905806347</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H8" s="2" t="str">
+      <c r="H8" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4258905806347,2.20484681868868","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R8" s="7" t="s">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="V8" s="0" t="str">
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="V8" s="1" t="str">
         <f aca="false">IF(AND(I8="",K8=""),IF(M8&lt;&gt;"",M8,""),IF(AND(I8&lt;&gt;"",K8=""),I8,IF(AND(I8="",K8&lt;&gt;""),K8,IF(ABS(J8-1)&lt;=ABS(13-L8),I8,K8))))</f>
         <v>0</v>
       </c>
-      <c r="W8" s="0" t="str">
+      <c r="W8" s="1" t="str">
         <f aca="false">IF(AND(O8="",Q8=""),IF(S8&lt;&gt;"",S8,""),IF(AND(O8&lt;&gt;"",Q8=""),O8,IF(AND(O8="",Q8&lt;&gt;""),Q8,IF(ABS(P8-1)&lt;=ABS(13-R8),O8,Q8))))</f>
         <v>0</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="1" t="n">
         <f aca="false">IF(OR(V8="",W8=""),"",
   IF(B8="ADD",AND(VALUE(V8)=1,VALUE(W8)=0),
     IF(B8="REMOVE",AND(VALUE(V8)=0,VALUE(W8)=1),
@@ -5030,64 +5038,64 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>2.13481716306763</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>41.3899769573627</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H9" s="2" t="str">
+      <c r="H9" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3899769573627,2.13481716306763","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="V9" s="0" t="str">
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="V9" s="1" t="str">
         <f aca="false">IF(AND(I9="",K9=""),IF(M9&lt;&gt;"",M9,""),IF(AND(I9&lt;&gt;"",K9=""),I9,IF(AND(I9="",K9&lt;&gt;""),K9,IF(ABS(J9-1)&lt;=ABS(13-L9),I9,K9))))</f>
         <v>0</v>
       </c>
-      <c r="W9" s="0" t="str">
+      <c r="W9" s="1" t="str">
         <f aca="false">IF(AND(O9="",Q9=""),IF(S9&lt;&gt;"",S9,""),IF(AND(O9&lt;&gt;"",Q9=""),O9,IF(AND(O9="",Q9&lt;&gt;""),Q9,IF(ABS(P9-1)&lt;=ABS(13-R9),O9,Q9))))</f>
         <v>0</v>
       </c>
-      <c r="X9" s="8" t="n">
+      <c r="X9" s="1" t="n">
         <f aca="false">IF(OR(V9="",W9=""),"",
   IF(B9="ADD",AND(VALUE(V9)=1,VALUE(W9)=0),
     IF(B9="REMOVE",AND(VALUE(V9)=0,VALUE(W9)=1),
@@ -5099,68 +5107,68 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>2.19752440653557</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>41.4192333717107</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H10" s="2" t="str">
+      <c r="H10" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4192333717107,2.19752440653557","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10" s="7" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="V10" s="0" t="str">
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="V10" s="1" t="str">
         <f aca="false">IF(AND(I10="",K10=""),IF(M10&lt;&gt;"",M10,""),IF(AND(I10&lt;&gt;"",K10=""),I10,IF(AND(I10="",K10&lt;&gt;""),K10,IF(ABS(J10-1)&lt;=ABS(13-L10),I10,K10))))</f>
         <v>0</v>
       </c>
-      <c r="W10" s="0" t="str">
+      <c r="W10" s="1" t="str">
         <f aca="false">IF(AND(O10="",Q10=""),IF(S10&lt;&gt;"",S10,""),IF(AND(O10&lt;&gt;"",Q10=""),O10,IF(AND(O10="",Q10&lt;&gt;""),Q10,IF(ABS(P10-1)&lt;=ABS(13-R10),O10,Q10))))</f>
         <v>0</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="1" t="n">
         <f aca="false">IF(OR(V10="",W10=""),"",
   IF(B10="ADD",AND(VALUE(V10)=1,VALUE(W10)=0),
     IF(B10="REMOVE",AND(VALUE(V10)=0,VALUE(W10)=1),
@@ -5172,56 +5180,56 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>2.20102627681254</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>41.4183372736594</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H11" s="2" t="str">
+      <c r="H11" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4183372736594,2.20102627681254","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R11" s="7" t="s">
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="V11" s="0" t="str">
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="V11" s="1" t="str">
         <f aca="false">IF(AND(I11="",K11=""),IF(M11&lt;&gt;"",M11,""),IF(AND(I11&lt;&gt;"",K11=""),I11,IF(AND(I11="",K11&lt;&gt;""),K11,IF(ABS(J11-1)&lt;=ABS(13-L11),I11,K11))))</f>
         <v/>
       </c>
-      <c r="W11" s="0" t="str">
+      <c r="W11" s="1" t="str">
         <f aca="false">IF(AND(O11="",Q11=""),IF(S11&lt;&gt;"",S11,""),IF(AND(O11&lt;&gt;"",Q11=""),O11,IF(AND(O11="",Q11&lt;&gt;""),Q11,IF(ABS(P11-1)&lt;=ABS(13-R11),O11,Q11))))</f>
         <v>0</v>
       </c>
-      <c r="X11" s="8" t="str">
+      <c r="X11" s="1" t="str">
         <f aca="false">IF(OR(V11="",W11=""),"",
   IF(B11="ADD",AND(VALUE(V11)=1,VALUE(W11)=0),
     IF(B11="REMOVE",AND(VALUE(V11)=0,VALUE(W11)=1),
@@ -5233,67 +5241,67 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>2.17167040591253</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>41.4161555680672</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H12" s="2" t="str">
+      <c r="H12" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4161555680672,2.17167040591253","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R12" s="7" t="s">
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="6" t="s">
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="V12" s="0" t="str">
+      <c r="V12" s="1" t="str">
         <f aca="false">IF(AND(I12="",K12=""),IF(M12&lt;&gt;"",M12,""),IF(AND(I12&lt;&gt;"",K12=""),I12,IF(AND(I12="",K12&lt;&gt;""),K12,IF(ABS(J12-1)&lt;=ABS(13-L12),I12,K12))))</f>
         <v>0</v>
       </c>
-      <c r="W12" s="0" t="str">
+      <c r="W12" s="1" t="str">
         <f aca="false">IF(AND(O12="",Q12=""),IF(S12&lt;&gt;"",S12,""),IF(AND(O12&lt;&gt;"",Q12=""),O12,IF(AND(O12="",Q12&lt;&gt;""),Q12,IF(ABS(P12-1)&lt;=ABS(13-R12),O12,Q12))))</f>
         <v>0</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="1" t="n">
         <f aca="false">IF(OR(V12="",W12=""),"",
   IF(B12="ADD",AND(VALUE(V12)=1,VALUE(W12)=0),
     IF(B12="REMOVE",AND(VALUE(V12)=0,VALUE(W12)=1),
@@ -5305,64 +5313,64 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>2.20786624678425</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>41.4210178011802</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H13" s="2" t="str">
+      <c r="H13" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4210178011802,2.20786624678425","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="7" t="s">
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="V13" s="0" t="str">
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="V13" s="1" t="str">
         <f aca="false">IF(AND(I13="",K13=""),IF(M13&lt;&gt;"",M13,""),IF(AND(I13&lt;&gt;"",K13=""),I13,IF(AND(I13="",K13&lt;&gt;""),K13,IF(ABS(J13-1)&lt;=ABS(13-L13),I13,K13))))</f>
         <v>0</v>
       </c>
-      <c r="W13" s="0" t="str">
+      <c r="W13" s="1" t="str">
         <f aca="false">IF(AND(O13="",Q13=""),IF(S13&lt;&gt;"",S13,""),IF(AND(O13&lt;&gt;"",Q13=""),O13,IF(AND(O13="",Q13&lt;&gt;""),Q13,IF(ABS(P13-1)&lt;=ABS(13-R13),O13,Q13))))</f>
         <v>0</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="1" t="n">
         <f aca="false">IF(OR(V13="",W13=""),"",
   IF(B13="ADD",AND(VALUE(V13)=1,VALUE(W13)=0),
     IF(B13="REMOVE",AND(VALUE(V13)=0,VALUE(W13)=1),
@@ -5374,68 +5382,68 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>2.16049369124227</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>41.4136824558834</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H14" s="2" t="str">
+      <c r="H14" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4136824558834,2.16049369124227","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="V14" s="0" t="str">
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="V14" s="1" t="str">
         <f aca="false">IF(AND(I14="",K14=""),IF(M14&lt;&gt;"",M14,""),IF(AND(I14&lt;&gt;"",K14=""),I14,IF(AND(I14="",K14&lt;&gt;""),K14,IF(ABS(J14-1)&lt;=ABS(13-L14),I14,K14))))</f>
         <v>0</v>
       </c>
-      <c r="W14" s="0" t="str">
+      <c r="W14" s="1" t="str">
         <f aca="false">IF(AND(O14="",Q14=""),IF(S14&lt;&gt;"",S14,""),IF(AND(O14&lt;&gt;"",Q14=""),O14,IF(AND(O14="",Q14&lt;&gt;""),Q14,IF(ABS(P14-1)&lt;=ABS(13-R14),O14,Q14))))</f>
         <v>0</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="1" t="n">
         <f aca="false">IF(OR(V14="",W14=""),"",
   IF(B14="ADD",AND(VALUE(V14)=1,VALUE(W14)=0),
     IF(B14="REMOVE",AND(VALUE(V14)=0,VALUE(W14)=1),
@@ -5447,64 +5455,64 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>2.19450094884008</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>41.3988457002622</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H15" s="2" t="str">
+      <c r="H15" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3988457002622,2.19450094884008","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="I15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="7" t="s">
+      <c r="K15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R15" s="7" t="s">
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="V15" s="0" t="str">
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="V15" s="1" t="str">
         <f aca="false">IF(AND(I15="",K15=""),IF(M15&lt;&gt;"",M15,""),IF(AND(I15&lt;&gt;"",K15=""),I15,IF(AND(I15="",K15&lt;&gt;""),K15,IF(ABS(J15-1)&lt;=ABS(13-L15),I15,K15))))</f>
         <v>0</v>
       </c>
-      <c r="W15" s="0" t="str">
+      <c r="W15" s="1" t="str">
         <f aca="false">IF(AND(O15="",Q15=""),IF(S15&lt;&gt;"",S15,""),IF(AND(O15&lt;&gt;"",Q15=""),O15,IF(AND(O15="",Q15&lt;&gt;""),Q15,IF(ABS(P15-1)&lt;=ABS(13-R15),O15,Q15))))</f>
         <v>0</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="1" t="n">
         <f aca="false">IF(OR(V15="",W15=""),"",
   IF(B15="ADD",AND(VALUE(V15)=1,VALUE(W15)=0),
     IF(B15="REMOVE",AND(VALUE(V15)=0,VALUE(W15)=1),
@@ -5516,71 +5524,71 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>2.17744010327688</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>41.3809929493489</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H16" s="2" t="str">
+      <c r="H16" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3809929493489,2.17744010327688","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" s="7" t="s">
+      <c r="K16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="7" t="s">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="6" t="s">
+      <c r="Q16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="V16" s="0" t="str">
+      <c r="V16" s="1" t="str">
         <f aca="false">IF(AND(I16="",K16=""),IF(M16&lt;&gt;"",M16,""),IF(AND(I16&lt;&gt;"",K16=""),I16,IF(AND(I16="",K16&lt;&gt;""),K16,IF(ABS(J16-1)&lt;=ABS(13-L16),I16,K16))))</f>
         <v>0</v>
       </c>
-      <c r="W16" s="0" t="str">
+      <c r="W16" s="1" t="str">
         <f aca="false">IF(AND(O16="",Q16=""),IF(S16&lt;&gt;"",S16,""),IF(AND(O16&lt;&gt;"",Q16=""),O16,IF(AND(O16="",Q16&lt;&gt;""),Q16,IF(ABS(P16-1)&lt;=ABS(13-R16),O16,Q16))))</f>
         <v>0</v>
       </c>
-      <c r="X16" s="8" t="n">
+      <c r="X16" s="1" t="n">
         <f aca="false">IF(OR(V16="",W16=""),"",
   IF(B16="ADD",AND(VALUE(V16)=1,VALUE(W16)=0),
     IF(B16="REMOVE",AND(VALUE(V16)=0,VALUE(W16)=1),
@@ -5592,60 +5600,60 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>2.20178666640468</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>41.3980884256415</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="H17" s="2" t="str">
+      <c r="H17" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3980884256415,2.20178666640468","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R17" s="7" t="s">
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="V17" s="0" t="str">
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="V17" s="1" t="str">
         <f aca="false">IF(AND(I17="",K17=""),IF(M17&lt;&gt;"",M17,""),IF(AND(I17&lt;&gt;"",K17=""),I17,IF(AND(I17="",K17&lt;&gt;""),K17,IF(ABS(J17-1)&lt;=ABS(13-L17),I17,K17))))</f>
         <v>0</v>
       </c>
-      <c r="W17" s="0" t="str">
+      <c r="W17" s="1" t="str">
         <f aca="false">IF(AND(O17="",Q17=""),IF(S17&lt;&gt;"",S17,""),IF(AND(O17&lt;&gt;"",Q17=""),O17,IF(AND(O17="",Q17&lt;&gt;""),Q17,IF(ABS(P17-1)&lt;=ABS(13-R17),O17,Q17))))</f>
         <v>0</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="X17" s="1" t="n">
         <f aca="false">IF(OR(V17="",W17=""),"",
   IF(B17="ADD",AND(VALUE(V17)=1,VALUE(W17)=0),
     IF(B17="REMOVE",AND(VALUE(V17)=0,VALUE(W17)=1),
@@ -5657,68 +5665,68 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>2.20466487047361</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>41.4076020157415</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H18" s="2" t="str">
+      <c r="H18" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4076020157415,2.20466487047361","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="K18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R18" s="7" t="s">
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="V18" s="0" t="str">
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="V18" s="1" t="str">
         <f aca="false">IF(AND(I18="",K18=""),IF(M18&lt;&gt;"",M18,""),IF(AND(I18&lt;&gt;"",K18=""),I18,IF(AND(I18="",K18&lt;&gt;""),K18,IF(ABS(J18-1)&lt;=ABS(13-L18),I18,K18))))</f>
         <v>1</v>
       </c>
-      <c r="W18" s="0" t="str">
+      <c r="W18" s="1" t="str">
         <f aca="false">IF(AND(O18="",Q18=""),IF(S18&lt;&gt;"",S18,""),IF(AND(O18&lt;&gt;"",Q18=""),O18,IF(AND(O18="",Q18&lt;&gt;""),Q18,IF(ABS(P18-1)&lt;=ABS(13-R18),O18,Q18))))</f>
         <v>1</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="X18" s="1" t="n">
         <f aca="false">IF(OR(V18="",W18=""),"",
   IF(B18="ADD",AND(VALUE(V18)=1,VALUE(W18)=0),
     IF(B18="REMOVE",AND(VALUE(V18)=0,VALUE(W18)=1),
@@ -5730,64 +5738,64 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>2.14699713630314</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <v>41.3760306038472</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H19" s="2" t="str">
+      <c r="H19" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3760306038472,2.14699713630314","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="7" t="s">
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="V19" s="0" t="str">
+      <c r="Q19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="V19" s="1" t="str">
         <f aca="false">IF(AND(I19="",K19=""),IF(M19&lt;&gt;"",M19,""),IF(AND(I19&lt;&gt;"",K19=""),I19,IF(AND(I19="",K19&lt;&gt;""),K19,IF(ABS(J19-1)&lt;=ABS(13-L19),I19,K19))))</f>
         <v>0</v>
       </c>
-      <c r="W19" s="0" t="str">
+      <c r="W19" s="1" t="str">
         <f aca="false">IF(AND(O19="",Q19=""),IF(S19&lt;&gt;"",S19,""),IF(AND(O19&lt;&gt;"",Q19=""),O19,IF(AND(O19="",Q19&lt;&gt;""),Q19,IF(ABS(P19-1)&lt;=ABS(13-R19),O19,Q19))))</f>
         <v>0</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="1" t="n">
         <f aca="false">IF(OR(V19="",W19=""),"",
   IF(B19="ADD",AND(VALUE(V19)=1,VALUE(W19)=0),
     IF(B19="REMOVE",AND(VALUE(V19)=0,VALUE(W19)=1),
@@ -5799,64 +5807,64 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>2.12152578919576</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>41.396619405733</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H20" s="2" t="str">
+      <c r="H20" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.396619405733,2.12152578919576","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P20" s="7" t="s">
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="V20" s="0" t="str">
+      <c r="Q20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="V20" s="1" t="str">
         <f aca="false">IF(AND(I20="",K20=""),IF(M20&lt;&gt;"",M20,""),IF(AND(I20&lt;&gt;"",K20=""),I20,IF(AND(I20="",K20&lt;&gt;""),K20,IF(ABS(J20-1)&lt;=ABS(13-L20),I20,K20))))</f>
         <v>0</v>
       </c>
-      <c r="W20" s="0" t="str">
+      <c r="W20" s="1" t="str">
         <f aca="false">IF(AND(O20="",Q20=""),IF(S20&lt;&gt;"",S20,""),IF(AND(O20&lt;&gt;"",Q20=""),O20,IF(AND(O20="",Q20&lt;&gt;""),Q20,IF(ABS(P20-1)&lt;=ABS(13-R20),O20,Q20))))</f>
         <v>0</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="1" t="n">
         <f aca="false">IF(OR(V20="",W20=""),"",
   IF(B20="ADD",AND(VALUE(V20)=1,VALUE(W20)=0),
     IF(B20="REMOVE",AND(VALUE(V20)=0,VALUE(W20)=1),
@@ -5868,68 +5876,68 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>2.17989992573641</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>41.4312265623016</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H21" s="2" t="str">
+      <c r="H21" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4312265623016,2.17989992573641","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="7" t="s">
+      <c r="I21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="K21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R21" s="7" t="s">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R21" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="V21" s="0" t="str">
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="V21" s="1" t="str">
         <f aca="false">IF(AND(I21="",K21=""),IF(M21&lt;&gt;"",M21,""),IF(AND(I21&lt;&gt;"",K21=""),I21,IF(AND(I21="",K21&lt;&gt;""),K21,IF(ABS(J21-1)&lt;=ABS(13-L21),I21,K21))))</f>
         <v>0</v>
       </c>
-      <c r="W21" s="0" t="str">
+      <c r="W21" s="1" t="str">
         <f aca="false">IF(AND(O21="",Q21=""),IF(S21&lt;&gt;"",S21,""),IF(AND(O21&lt;&gt;"",Q21=""),O21,IF(AND(O21="",Q21&lt;&gt;""),Q21,IF(ABS(P21-1)&lt;=ABS(13-R21),O21,Q21))))</f>
         <v>0</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="X21" s="1" t="n">
         <f aca="false">IF(OR(V21="",W21=""),"",
   IF(B21="ADD",AND(VALUE(V21)=1,VALUE(W21)=0),
     IF(B21="REMOVE",AND(VALUE(V21)=0,VALUE(W21)=1),
@@ -5941,64 +5949,64 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <v>2.1257689815069</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <v>41.3929009079565</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H22" s="2" t="str">
+      <c r="H22" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3929009079565,2.1257689815069","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P22" s="7" t="s">
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q22" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="V22" s="0" t="str">
+      <c r="Q22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="V22" s="1" t="str">
         <f aca="false">IF(AND(I22="",K22=""),IF(M22&lt;&gt;"",M22,""),IF(AND(I22&lt;&gt;"",K22=""),I22,IF(AND(I22="",K22&lt;&gt;""),K22,IF(ABS(J22-1)&lt;=ABS(13-L22),I22,K22))))</f>
         <v>0</v>
       </c>
-      <c r="W22" s="0" t="str">
+      <c r="W22" s="1" t="str">
         <f aca="false">IF(AND(O22="",Q22=""),IF(S22&lt;&gt;"",S22,""),IF(AND(O22&lt;&gt;"",Q22=""),O22,IF(AND(O22="",Q22&lt;&gt;""),Q22,IF(ABS(P22-1)&lt;=ABS(13-R22),O22,Q22))))</f>
         <v>0</v>
       </c>
-      <c r="X22" s="8" t="n">
+      <c r="X22" s="1" t="n">
         <f aca="false">IF(OR(V22="",W22=""),"",
   IF(B22="ADD",AND(VALUE(V22)=1,VALUE(W22)=0),
     IF(B22="REMOVE",AND(VALUE(V22)=0,VALUE(W22)=1),
@@ -6010,60 +6018,60 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>2.18508949253952</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="1" t="n">
         <v>41.4345475359841</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H23" s="2" t="str">
+      <c r="H23" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4345475359841,2.18508949253952","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="7" t="s">
+      <c r="I23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P23" s="7" t="s">
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="V23" s="0" t="str">
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="V23" s="1" t="str">
         <f aca="false">IF(AND(I23="",K23=""),IF(M23&lt;&gt;"",M23,""),IF(AND(I23&lt;&gt;"",K23=""),I23,IF(AND(I23="",K23&lt;&gt;""),K23,IF(ABS(J23-1)&lt;=ABS(13-L23),I23,K23))))</f>
         <v>0</v>
       </c>
-      <c r="W23" s="0" t="str">
+      <c r="W23" s="1" t="str">
         <f aca="false">IF(AND(O23="",Q23=""),IF(S23&lt;&gt;"",S23,""),IF(AND(O23&lt;&gt;"",Q23=""),O23,IF(AND(O23="",Q23&lt;&gt;""),Q23,IF(ABS(P23-1)&lt;=ABS(13-R23),O23,Q23))))</f>
         <v>0</v>
       </c>
-      <c r="X23" s="8" t="n">
+      <c r="X23" s="1" t="n">
         <f aca="false">IF(OR(V23="",W23=""),"",
   IF(B23="ADD",AND(VALUE(V23)=1,VALUE(W23)=0),
     IF(B23="REMOVE",AND(VALUE(V23)=0,VALUE(W23)=1),
@@ -6075,68 +6083,68 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>2.17554070368043</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <v>41.4280696452023</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H24" s="2" t="str">
+      <c r="H24" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4280696452023,2.17554070368043","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7" t="s">
+      <c r="I24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="K24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R24" s="7" t="s">
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="V24" s="0" t="str">
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="V24" s="1" t="str">
         <f aca="false">IF(AND(I24="",K24=""),IF(M24&lt;&gt;"",M24,""),IF(AND(I24&lt;&gt;"",K24=""),I24,IF(AND(I24="",K24&lt;&gt;""),K24,IF(ABS(J24-1)&lt;=ABS(13-L24),I24,K24))))</f>
         <v>1</v>
       </c>
-      <c r="W24" s="0" t="str">
+      <c r="W24" s="1" t="str">
         <f aca="false">IF(AND(O24="",Q24=""),IF(S24&lt;&gt;"",S24,""),IF(AND(O24&lt;&gt;"",Q24=""),O24,IF(AND(O24="",Q24&lt;&gt;""),Q24,IF(ABS(P24-1)&lt;=ABS(13-R24),O24,Q24))))</f>
         <v>1</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="1" t="n">
         <f aca="false">IF(OR(V24="",W24=""),"",
   IF(B24="ADD",AND(VALUE(V24)=1,VALUE(W24)=0),
     IF(B24="REMOVE",AND(VALUE(V24)=0,VALUE(W24)=1),
@@ -6148,64 +6156,64 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>2.18993300624021</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <v>41.4420740636848</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="G25" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H25" s="2" t="str">
+      <c r="H25" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4420740636848,2.18993300624021","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7" t="s">
+      <c r="I25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" s="7" t="s">
+      <c r="K25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R25" s="7" t="s">
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="V25" s="0" t="str">
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="V25" s="1" t="str">
         <f aca="false">IF(AND(I25="",K25=""),IF(M25&lt;&gt;"",M25,""),IF(AND(I25&lt;&gt;"",K25=""),I25,IF(AND(I25="",K25&lt;&gt;""),K25,IF(ABS(J25-1)&lt;=ABS(13-L25),I25,K25))))</f>
         <v>0</v>
       </c>
-      <c r="W25" s="0" t="str">
+      <c r="W25" s="1" t="str">
         <f aca="false">IF(AND(O25="",Q25=""),IF(S25&lt;&gt;"",S25,""),IF(AND(O25&lt;&gt;"",Q25=""),O25,IF(AND(O25="",Q25&lt;&gt;""),Q25,IF(ABS(P25-1)&lt;=ABS(13-R25),O25,Q25))))</f>
         <v>0</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="1" t="n">
         <f aca="false">IF(OR(V25="",W25=""),"",
   IF(B25="ADD",AND(VALUE(V25)=1,VALUE(W25)=0),
     IF(B25="REMOVE",AND(VALUE(V25)=0,VALUE(W25)=1),
@@ -6217,64 +6225,64 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <v>2.15217129410179</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <v>41.4015813026278</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="H26" s="2" t="str">
+      <c r="H26" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4015813026278,2.15217129410179","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26" s="7" t="s">
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P26" s="7" t="s">
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="V26" s="0" t="str">
+      <c r="Q26" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="V26" s="1" t="str">
         <f aca="false">IF(AND(I26="",K26=""),IF(M26&lt;&gt;"",M26,""),IF(AND(I26&lt;&gt;"",K26=""),I26,IF(AND(I26="",K26&lt;&gt;""),K26,IF(ABS(J26-1)&lt;=ABS(13-L26),I26,K26))))</f>
         <v>0</v>
       </c>
-      <c r="W26" s="0" t="str">
+      <c r="W26" s="1" t="str">
         <f aca="false">IF(AND(O26="",Q26=""),IF(S26&lt;&gt;"",S26,""),IF(AND(O26&lt;&gt;"",Q26=""),O26,IF(AND(O26="",Q26&lt;&gt;""),Q26,IF(ABS(P26-1)&lt;=ABS(13-R26),O26,Q26))))</f>
         <v>0</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="1" t="n">
         <f aca="false">IF(OR(V26="",W26=""),"",
   IF(B26="ADD",AND(VALUE(V26)=1,VALUE(W26)=0),
     IF(B26="REMOVE",AND(VALUE(V26)=0,VALUE(W26)=1),
@@ -6286,64 +6294,64 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>2.13682274790633</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <v>41.4006579623741</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="G27" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H27" s="2" t="str">
+      <c r="H27" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4006579623741,2.13682274790633","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P27" s="7" t="s">
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="V27" s="0" t="str">
+      <c r="Q27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="V27" s="1" t="str">
         <f aca="false">IF(AND(I27="",K27=""),IF(M27&lt;&gt;"",M27,""),IF(AND(I27&lt;&gt;"",K27=""),I27,IF(AND(I27="",K27&lt;&gt;""),K27,IF(ABS(J27-1)&lt;=ABS(13-L27),I27,K27))))</f>
         <v>0</v>
       </c>
-      <c r="W27" s="0" t="str">
+      <c r="W27" s="1" t="str">
         <f aca="false">IF(AND(O27="",Q27=""),IF(S27&lt;&gt;"",S27,""),IF(AND(O27&lt;&gt;"",Q27=""),O27,IF(AND(O27="",Q27&lt;&gt;""),Q27,IF(ABS(P27-1)&lt;=ABS(13-R27),O27,Q27))))</f>
         <v>0</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="X27" s="1" t="n">
         <f aca="false">IF(OR(V27="",W27=""),"",
   IF(B27="ADD",AND(VALUE(V27)=1,VALUE(W27)=0),
     IF(B27="REMOVE",AND(VALUE(V27)=0,VALUE(W27)=1),
@@ -6355,71 +6363,71 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <v>2.17278778456154</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="F28" s="1" t="n">
         <v>41.4228160913898</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="G28" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H28" s="2" t="str">
+      <c r="H28" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4228160913898,2.17278778456154","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" s="7" t="s">
+      <c r="I28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L28" s="7" t="s">
+      <c r="K28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R28" s="7" t="s">
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="6" t="s">
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="V28" s="0" t="str">
+      <c r="V28" s="1" t="str">
         <f aca="false">IF(AND(I28="",K28=""),IF(M28&lt;&gt;"",M28,""),IF(AND(I28&lt;&gt;"",K28=""),I28,IF(AND(I28="",K28&lt;&gt;""),K28,IF(ABS(J28-1)&lt;=ABS(13-L28),I28,K28))))</f>
         <v>0</v>
       </c>
-      <c r="W28" s="0" t="str">
+      <c r="W28" s="1" t="str">
         <f aca="false">IF(AND(O28="",Q28=""),IF(S28&lt;&gt;"",S28,""),IF(AND(O28&lt;&gt;"",Q28=""),O28,IF(AND(O28="",Q28&lt;&gt;""),Q28,IF(ABS(P28-1)&lt;=ABS(13-R28),O28,Q28))))</f>
         <v>0</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="X28" s="1" t="n">
         <f aca="false">IF(OR(V28="",W28=""),"",
   IF(B28="ADD",AND(VALUE(V28)=1,VALUE(W28)=0),
     IF(B28="REMOVE",AND(VALUE(V28)=0,VALUE(W28)=1),
@@ -6431,64 +6439,64 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <v>2.1846385508759</v>
       </c>
-      <c r="F29" s="0" t="n">
+      <c r="F29" s="1" t="n">
         <v>41.4142083506803</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="G29" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H29" s="2" t="str">
+      <c r="H29" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4142083506803,2.1846385508759","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="7" t="s">
+      <c r="I29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="V29" s="0" t="str">
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="V29" s="1" t="str">
         <f aca="false">IF(AND(I29="",K29=""),IF(M29&lt;&gt;"",M29,""),IF(AND(I29&lt;&gt;"",K29=""),I29,IF(AND(I29="",K29&lt;&gt;""),K29,IF(ABS(J29-1)&lt;=ABS(13-L29),I29,K29))))</f>
         <v>0</v>
       </c>
-      <c r="W29" s="0" t="str">
+      <c r="W29" s="1" t="str">
         <f aca="false">IF(AND(O29="",Q29=""),IF(S29&lt;&gt;"",S29,""),IF(AND(O29&lt;&gt;"",Q29=""),O29,IF(AND(O29="",Q29&lt;&gt;""),Q29,IF(ABS(P29-1)&lt;=ABS(13-R29),O29,Q29))))</f>
         <v>0</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="1" t="n">
         <f aca="false">IF(OR(V29="",W29=""),"",
   IF(B29="ADD",AND(VALUE(V29)=1,VALUE(W29)=0),
     IF(B29="REMOVE",AND(VALUE(V29)=0,VALUE(W29)=1),
@@ -6500,67 +6508,67 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="1" t="n">
         <v>2.15654792103243</v>
       </c>
-      <c r="F30" s="0" t="n">
+      <c r="F30" s="1" t="n">
         <v>41.4063712780874</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="G30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="H30" s="2" t="str">
+      <c r="H30" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4063712780874,2.15654792103243","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="7" t="s">
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P30" s="7" t="s">
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R30" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="6" t="s">
+      <c r="Q30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="V30" s="0" t="str">
+      <c r="V30" s="1" t="str">
         <f aca="false">IF(AND(I30="",K30=""),IF(M30&lt;&gt;"",M30,""),IF(AND(I30&lt;&gt;"",K30=""),I30,IF(AND(I30="",K30&lt;&gt;""),K30,IF(ABS(J30-1)&lt;=ABS(13-L30),I30,K30))))</f>
         <v>0</v>
       </c>
-      <c r="W30" s="0" t="str">
+      <c r="W30" s="1" t="str">
         <f aca="false">IF(AND(O30="",Q30=""),IF(S30&lt;&gt;"",S30,""),IF(AND(O30&lt;&gt;"",Q30=""),O30,IF(AND(O30="",Q30&lt;&gt;""),Q30,IF(ABS(P30-1)&lt;=ABS(13-R30),O30,Q30))))</f>
         <v>0</v>
       </c>
-      <c r="X30" s="8" t="n">
+      <c r="X30" s="1" t="n">
         <f aca="false">IF(OR(V30="",W30=""),"",
   IF(B30="ADD",AND(VALUE(V30)=1,VALUE(W30)=0),
     IF(B30="REMOVE",AND(VALUE(V30)=0,VALUE(W30)=1),
@@ -6572,67 +6580,67 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="1" t="n">
         <v>2.13622558148501</v>
       </c>
-      <c r="F31" s="0" t="n">
+      <c r="F31" s="1" t="n">
         <v>41.3868869775373</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="G31" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H31" s="2" t="str">
+      <c r="H31" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3868869775373,2.13622558148501","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="7" t="s">
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P31" s="7" t="s">
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q31" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="6" t="s">
+      <c r="Q31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="V31" s="0" t="str">
+      <c r="V31" s="1" t="str">
         <f aca="false">IF(AND(I31="",K31=""),IF(M31&lt;&gt;"",M31,""),IF(AND(I31&lt;&gt;"",K31=""),I31,IF(AND(I31="",K31&lt;&gt;""),K31,IF(ABS(J31-1)&lt;=ABS(13-L31),I31,K31))))</f>
         <v>0</v>
       </c>
-      <c r="W31" s="0" t="str">
+      <c r="W31" s="1" t="str">
         <f aca="false">IF(AND(O31="",Q31=""),IF(S31&lt;&gt;"",S31,""),IF(AND(O31&lt;&gt;"",Q31=""),O31,IF(AND(O31="",Q31&lt;&gt;""),Q31,IF(ABS(P31-1)&lt;=ABS(13-R31),O31,Q31))))</f>
         <v>0</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="1" t="n">
         <f aca="false">IF(OR(V31="",W31=""),"",
   IF(B31="ADD",AND(VALUE(V31)=1,VALUE(W31)=0),
     IF(B31="REMOVE",AND(VALUE(V31)=0,VALUE(W31)=1),
@@ -6644,68 +6652,68 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="0" t="s">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="1" t="n">
         <v>2.1845963289228</v>
       </c>
-      <c r="F32" s="0" t="n">
+      <c r="F32" s="1" t="n">
         <v>41.3914544159587</v>
       </c>
-      <c r="G32" s="0" t="s">
+      <c r="G32" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H32" s="2" t="str">
+      <c r="H32" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3914544159587,2.1845963289228","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="7" t="s">
+      <c r="I32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" s="7" t="s">
+      <c r="K32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P32" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R32" s="7" t="s">
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R32" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="V32" s="0" t="str">
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="V32" s="1" t="str">
         <f aca="false">IF(AND(I32="",K32=""),IF(M32&lt;&gt;"",M32,""),IF(AND(I32&lt;&gt;"",K32=""),I32,IF(AND(I32="",K32&lt;&gt;""),K32,IF(ABS(J32-1)&lt;=ABS(13-L32),I32,K32))))</f>
         <v>0</v>
       </c>
-      <c r="W32" s="0" t="str">
+      <c r="W32" s="1" t="str">
         <f aca="false">IF(AND(O32="",Q32=""),IF(S32&lt;&gt;"",S32,""),IF(AND(O32&lt;&gt;"",Q32=""),O32,IF(AND(O32="",Q32&lt;&gt;""),Q32,IF(ABS(P32-1)&lt;=ABS(13-R32),O32,Q32))))</f>
         <v>0</v>
       </c>
-      <c r="X32" s="8" t="n">
+      <c r="X32" s="1" t="n">
         <f aca="false">IF(OR(V32="",W32=""),"",
   IF(B32="ADD",AND(VALUE(V32)=1,VALUE(W32)=0),
     IF(B32="REMOVE",AND(VALUE(V32)=0,VALUE(W32)=1),
@@ -6717,68 +6725,68 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="0" t="s">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <v>2.20243115228888</v>
       </c>
-      <c r="F33" s="0" t="n">
+      <c r="F33" s="1" t="n">
         <v>41.400307900951</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H33" s="2" t="str">
+      <c r="H33" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.400307900951,2.20243115228888","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="7" t="s">
+      <c r="I33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" s="7" t="s">
+      <c r="K33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="V33" s="0" t="str">
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="V33" s="1" t="str">
         <f aca="false">IF(AND(I33="",K33=""),IF(M33&lt;&gt;"",M33,""),IF(AND(I33&lt;&gt;"",K33=""),I33,IF(AND(I33="",K33&lt;&gt;""),K33,IF(ABS(J33-1)&lt;=ABS(13-L33),I33,K33))))</f>
         <v>0</v>
       </c>
-      <c r="W33" s="0" t="str">
+      <c r="W33" s="1" t="str">
         <f aca="false">IF(AND(O33="",Q33=""),IF(S33&lt;&gt;"",S33,""),IF(AND(O33&lt;&gt;"",Q33=""),O33,IF(AND(O33="",Q33&lt;&gt;""),Q33,IF(ABS(P33-1)&lt;=ABS(13-R33),O33,Q33))))</f>
         <v>0</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="1" t="n">
         <f aca="false">IF(OR(V33="",W33=""),"",
   IF(B33="ADD",AND(VALUE(V33)=1,VALUE(W33)=0),
     IF(B33="REMOVE",AND(VALUE(V33)=0,VALUE(W33)=1),
@@ -6790,64 +6798,64 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <v>2.19163916237013</v>
       </c>
-      <c r="F34" s="0" t="n">
+      <c r="F34" s="1" t="n">
         <v>41.3796612123254</v>
       </c>
-      <c r="G34" s="0" t="s">
+      <c r="G34" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="2" t="str">
+      <c r="H34" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3796612123254,2.19163916237013","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="7" t="s">
+      <c r="I34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L34" s="7" t="s">
+      <c r="K34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R34" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="V34" s="0" t="str">
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="V34" s="1" t="str">
         <f aca="false">IF(AND(I34="",K34=""),IF(M34&lt;&gt;"",M34,""),IF(AND(I34&lt;&gt;"",K34=""),I34,IF(AND(I34="",K34&lt;&gt;""),K34,IF(ABS(J34-1)&lt;=ABS(13-L34),I34,K34))))</f>
         <v>0</v>
       </c>
-      <c r="W34" s="0" t="str">
+      <c r="W34" s="1" t="str">
         <f aca="false">IF(AND(O34="",Q34=""),IF(S34&lt;&gt;"",S34,""),IF(AND(O34&lt;&gt;"",Q34=""),O34,IF(AND(O34="",Q34&lt;&gt;""),Q34,IF(ABS(P34-1)&lt;=ABS(13-R34),O34,Q34))))</f>
         <v>0</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="1" t="n">
         <f aca="false">IF(OR(V34="",W34=""),"",
   IF(B34="ADD",AND(VALUE(V34)=1,VALUE(W34)=0),
     IF(B34="REMOVE",AND(VALUE(V34)=0,VALUE(W34)=1),
@@ -6859,68 +6867,68 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="0" t="s">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <v>2.18047713982976</v>
       </c>
-      <c r="F35" s="0" t="n">
+      <c r="F35" s="1" t="n">
         <v>41.3853426556678</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="G35" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H35" s="2" t="str">
+      <c r="H35" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3853426556678,2.18047713982976","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J35" s="7" t="s">
+      <c r="I35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="V35" s="0" t="str">
+      <c r="K35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="V35" s="1" t="str">
         <f aca="false">IF(AND(I35="",K35=""),IF(M35&lt;&gt;"",M35,""),IF(AND(I35&lt;&gt;"",K35=""),I35,IF(AND(I35="",K35&lt;&gt;""),K35,IF(ABS(J35-1)&lt;=ABS(13-L35),I35,K35))))</f>
         <v>0</v>
       </c>
-      <c r="W35" s="0" t="str">
+      <c r="W35" s="1" t="str">
         <f aca="false">IF(AND(O35="",Q35=""),IF(S35&lt;&gt;"",S35,""),IF(AND(O35&lt;&gt;"",Q35=""),O35,IF(AND(O35="",Q35&lt;&gt;""),Q35,IF(ABS(P35-1)&lt;=ABS(13-R35),O35,Q35))))</f>
         <v>0</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="1" t="n">
         <f aca="false">IF(OR(V35="",W35=""),"",
   IF(B35="ADD",AND(VALUE(V35)=1,VALUE(W35)=0),
     IF(B35="REMOVE",AND(VALUE(V35)=0,VALUE(W35)=1),
@@ -6932,64 +6940,64 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <v>2.15487410700261</v>
       </c>
-      <c r="F36" s="0" t="n">
+      <c r="F36" s="1" t="n">
         <v>41.3981411820391</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H36" s="2" t="str">
+      <c r="H36" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3981411820391,2.15487410700261","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" s="7" t="s">
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P36" s="7" t="s">
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R36" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="V36" s="0" t="str">
+      <c r="Q36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="V36" s="1" t="str">
         <f aca="false">IF(AND(I36="",K36=""),IF(M36&lt;&gt;"",M36,""),IF(AND(I36&lt;&gt;"",K36=""),I36,IF(AND(I36="",K36&lt;&gt;""),K36,IF(ABS(J36-1)&lt;=ABS(13-L36),I36,K36))))</f>
         <v>0</v>
       </c>
-      <c r="W36" s="0" t="str">
+      <c r="W36" s="1" t="str">
         <f aca="false">IF(AND(O36="",Q36=""),IF(S36&lt;&gt;"",S36,""),IF(AND(O36&lt;&gt;"",Q36=""),O36,IF(AND(O36="",Q36&lt;&gt;""),Q36,IF(ABS(P36-1)&lt;=ABS(13-R36),O36,Q36))))</f>
         <v>0</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="1" t="n">
         <f aca="false">IF(OR(V36="",W36=""),"",
   IF(B36="ADD",AND(VALUE(V36)=1,VALUE(W36)=0),
     IF(B36="REMOVE",AND(VALUE(V36)=0,VALUE(W36)=1),
@@ -7001,64 +7009,64 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <v>2.14114720156026</v>
       </c>
-      <c r="F37" s="0" t="n">
+      <c r="F37" s="1" t="n">
         <v>41.4102699004482</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H37" s="2" t="str">
+      <c r="H37" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4102699004482,2.14114720156026","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N37" s="7" t="s">
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="O37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P37" s="7" t="s">
+      <c r="O37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="V37" s="0" t="str">
+      <c r="Q37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R37" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S37" s="8"/>
+      <c r="T37" s="8"/>
+      <c r="V37" s="1" t="str">
         <f aca="false">IF(AND(I37="",K37=""),IF(M37&lt;&gt;"",M37,""),IF(AND(I37&lt;&gt;"",K37=""),I37,IF(AND(I37="",K37&lt;&gt;""),K37,IF(ABS(J37-1)&lt;=ABS(13-L37),I37,K37))))</f>
         <v>0</v>
       </c>
-      <c r="W37" s="0" t="str">
+      <c r="W37" s="1" t="str">
         <f aca="false">IF(AND(O37="",Q37=""),IF(S37&lt;&gt;"",S37,""),IF(AND(O37&lt;&gt;"",Q37=""),O37,IF(AND(O37="",Q37&lt;&gt;""),Q37,IF(ABS(P37-1)&lt;=ABS(13-R37),O37,Q37))))</f>
         <v>0</v>
       </c>
-      <c r="X37" s="8" t="n">
+      <c r="X37" s="1" t="n">
         <f aca="false">IF(OR(V37="",W37=""),"",
   IF(B37="ADD",AND(VALUE(V37)=1,VALUE(W37)=0),
     IF(B37="REMOVE",AND(VALUE(V37)=0,VALUE(W37)=1),
@@ -7070,68 +7078,68 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <v>2.17240513302861</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="1" t="n">
         <v>41.426135711319</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="2" t="str">
+      <c r="H38" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.426135711319,2.17240513302861","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="7" t="s">
+      <c r="I38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L38" s="7" t="s">
+      <c r="K38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P38" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R38" s="7" t="s">
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="V38" s="0" t="str">
+      <c r="S38" s="8"/>
+      <c r="T38" s="8"/>
+      <c r="V38" s="1" t="str">
         <f aca="false">IF(AND(I38="",K38=""),IF(M38&lt;&gt;"",M38,""),IF(AND(I38&lt;&gt;"",K38=""),I38,IF(AND(I38="",K38&lt;&gt;""),K38,IF(ABS(J38-1)&lt;=ABS(13-L38),I38,K38))))</f>
         <v>0</v>
       </c>
-      <c r="W38" s="0" t="str">
+      <c r="W38" s="1" t="str">
         <f aca="false">IF(AND(O38="",Q38=""),IF(S38&lt;&gt;"",S38,""),IF(AND(O38&lt;&gt;"",Q38=""),O38,IF(AND(O38="",Q38&lt;&gt;""),Q38,IF(ABS(P38-1)&lt;=ABS(13-R38),O38,Q38))))</f>
         <v>0</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="1" t="n">
         <f aca="false">IF(OR(V38="",W38=""),"",
   IF(B38="ADD",AND(VALUE(V38)=1,VALUE(W38)=0),
     IF(B38="REMOVE",AND(VALUE(V38)=0,VALUE(W38)=1),
@@ -7143,64 +7151,64 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <v>2.17435088704027</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="1" t="n">
         <v>41.4370155099029</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H39" s="2" t="str">
+      <c r="H39" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4370155099029,2.17435088704027","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N39" s="7" t="s">
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N39" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="O39" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P39" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q39" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R39" s="7" t="s">
+      <c r="O39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P39" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R39" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="V39" s="0" t="str">
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="V39" s="1" t="str">
         <f aca="false">IF(AND(I39="",K39=""),IF(M39&lt;&gt;"",M39,""),IF(AND(I39&lt;&gt;"",K39=""),I39,IF(AND(I39="",K39&lt;&gt;""),K39,IF(ABS(J39-1)&lt;=ABS(13-L39),I39,K39))))</f>
         <v>0</v>
       </c>
-      <c r="W39" s="0" t="str">
+      <c r="W39" s="1" t="str">
         <f aca="false">IF(AND(O39="",Q39=""),IF(S39&lt;&gt;"",S39,""),IF(AND(O39&lt;&gt;"",Q39=""),O39,IF(AND(O39="",Q39&lt;&gt;""),Q39,IF(ABS(P39-1)&lt;=ABS(13-R39),O39,Q39))))</f>
         <v>0</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="1" t="n">
         <f aca="false">IF(OR(V39="",W39=""),"",
   IF(B39="ADD",AND(VALUE(V39)=1,VALUE(W39)=0),
     IF(B39="REMOVE",AND(VALUE(V39)=0,VALUE(W39)=1),
@@ -7212,68 +7220,68 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <v>2.172146050328</v>
       </c>
-      <c r="F40" s="0" t="n">
+      <c r="F40" s="1" t="n">
         <v>41.4283525000278</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="H40" s="2" t="str">
+      <c r="H40" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4283525000278,2.172146050328","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" s="7" t="s">
+      <c r="I40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L40" s="7" t="s">
+      <c r="K40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P40" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q40" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R40" s="7" t="s">
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R40" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="V40" s="0" t="str">
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="V40" s="1" t="str">
         <f aca="false">IF(AND(I40="",K40=""),IF(M40&lt;&gt;"",M40,""),IF(AND(I40&lt;&gt;"",K40=""),I40,IF(AND(I40="",K40&lt;&gt;""),K40,IF(ABS(J40-1)&lt;=ABS(13-L40),I40,K40))))</f>
         <v>0</v>
       </c>
-      <c r="W40" s="0" t="str">
+      <c r="W40" s="1" t="str">
         <f aca="false">IF(AND(O40="",Q40=""),IF(S40&lt;&gt;"",S40,""),IF(AND(O40&lt;&gt;"",Q40=""),O40,IF(AND(O40="",Q40&lt;&gt;""),Q40,IF(ABS(P40-1)&lt;=ABS(13-R40),O40,Q40))))</f>
         <v>0</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="1" t="n">
         <f aca="false">IF(OR(V40="",W40=""),"",
   IF(B40="ADD",AND(VALUE(V40)=1,VALUE(W40)=0),
     IF(B40="REMOVE",AND(VALUE(V40)=0,VALUE(W40)=1),
@@ -7285,68 +7293,68 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <v>2.12577009757984</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="1" t="n">
         <v>41.37663481171</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="G41" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H41" s="2" t="str">
+      <c r="H41" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.37663481171,2.12577009757984","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="7" t="s">
+      <c r="I41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P41" s="7" t="s">
+      <c r="K41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P41" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q41" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R41" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="V41" s="0" t="str">
+      <c r="Q41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="V41" s="1" t="str">
         <f aca="false">IF(AND(I41="",K41=""),IF(M41&lt;&gt;"",M41,""),IF(AND(I41&lt;&gt;"",K41=""),I41,IF(AND(I41="",K41&lt;&gt;""),K41,IF(ABS(J41-1)&lt;=ABS(13-L41),I41,K41))))</f>
         <v>0</v>
       </c>
-      <c r="W41" s="0" t="str">
+      <c r="W41" s="1" t="str">
         <f aca="false">IF(AND(O41="",Q41=""),IF(S41&lt;&gt;"",S41,""),IF(AND(O41&lt;&gt;"",Q41=""),O41,IF(AND(O41="",Q41&lt;&gt;""),Q41,IF(ABS(P41-1)&lt;=ABS(13-R41),O41,Q41))))</f>
         <v>0</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="1" t="n">
         <f aca="false">IF(OR(V41="",W41=""),"",
   IF(B41="ADD",AND(VALUE(V41)=1,VALUE(W41)=0),
     IF(B41="REMOVE",AND(VALUE(V41)=0,VALUE(W41)=1),
@@ -7358,68 +7366,68 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="1" t="n">
         <v>2.18477301094056</v>
       </c>
-      <c r="F42" s="0" t="n">
+      <c r="F42" s="1" t="n">
         <v>41.4254559968539</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H42" s="2" t="str">
+      <c r="H42" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4254559968539,2.18477301094056","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I42" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J42" s="7" t="s">
+      <c r="I42" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K42" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L42" s="7" t="s">
+      <c r="K42" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P42" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q42" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R42" s="7" t="s">
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q42" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R42" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="V42" s="0" t="str">
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="V42" s="1" t="str">
         <f aca="false">IF(AND(I42="",K42=""),IF(M42&lt;&gt;"",M42,""),IF(AND(I42&lt;&gt;"",K42=""),I42,IF(AND(I42="",K42&lt;&gt;""),K42,IF(ABS(J42-1)&lt;=ABS(13-L42),I42,K42))))</f>
         <v>0</v>
       </c>
-      <c r="W42" s="0" t="str">
+      <c r="W42" s="1" t="str">
         <f aca="false">IF(AND(O42="",Q42=""),IF(S42&lt;&gt;"",S42,""),IF(AND(O42&lt;&gt;"",Q42=""),O42,IF(AND(O42="",Q42&lt;&gt;""),Q42,IF(ABS(P42-1)&lt;=ABS(13-R42),O42,Q42))))</f>
         <v>0</v>
       </c>
-      <c r="X42" s="8" t="n">
+      <c r="X42" s="1" t="n">
         <f aca="false">IF(OR(V42="",W42=""),"",
   IF(B42="ADD",AND(VALUE(V42)=1,VALUE(W42)=0),
     IF(B42="REMOVE",AND(VALUE(V42)=0,VALUE(W42)=1),
@@ -7431,56 +7439,56 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="1" t="n">
         <v>2.13260915679332</v>
       </c>
-      <c r="F43" s="0" t="n">
+      <c r="F43" s="1" t="n">
         <v>41.3745912972665</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H43" s="2" t="str">
+      <c r="H43" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3745912972665,2.13260915679332","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="M43" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N43" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R43" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="V43" s="0" t="str">
+      <c r="M43" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S43" s="8"/>
+      <c r="T43" s="8"/>
+      <c r="V43" s="1" t="str">
         <f aca="false">IF(AND(I46="",K46=""),IF(M43&lt;&gt;"",M43,""),IF(AND(I46&lt;&gt;"",K46=""),I46,IF(AND(I46="",K46&lt;&gt;""),K46,IF(ABS(J46-1)&lt;=ABS(13-L46),I46,K46))))</f>
         <v>0</v>
       </c>
-      <c r="W43" s="0" t="str">
+      <c r="W43" s="1" t="str">
         <f aca="false">IF(AND(O43="",Q43=""),IF(S43&lt;&gt;"",S43,""),IF(AND(O43&lt;&gt;"",Q43=""),O43,IF(AND(O43="",Q43&lt;&gt;""),Q43,IF(ABS(P43-1)&lt;=ABS(13-R43),O43,Q43))))</f>
         <v>0</v>
       </c>
-      <c r="X43" s="8" t="n">
+      <c r="X43" s="1" t="n">
         <f aca="false">IF(OR(V43="",W43=""),"",
   IF(B43="ADD",AND(VALUE(V43)=1,VALUE(W43)=0),
     IF(B43="REMOVE",AND(VALUE(V43)=0,VALUE(W43)=1),
@@ -7492,64 +7500,64 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <v>2.17998387981679</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="1" t="n">
         <v>41.4130107880215</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H44" s="2" t="str">
+      <c r="H44" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4130107880215,2.17998387981679","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P44" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q44" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R44" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="V44" s="0" t="str">
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q44" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R44" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S44" s="8"/>
+      <c r="T44" s="8"/>
+      <c r="V44" s="1" t="str">
         <f aca="false">IF(AND(I44="",K44=""),IF(M44&lt;&gt;"",M44,""),IF(AND(I44&lt;&gt;"",K44=""),I44,IF(AND(I44="",K44&lt;&gt;""),K44,IF(ABS(J44-1)&lt;=ABS(13-L44),I44,K44))))</f>
         <v>0</v>
       </c>
-      <c r="W44" s="0" t="str">
+      <c r="W44" s="1" t="str">
         <f aca="false">IF(AND(O44="",Q44=""),IF(S44&lt;&gt;"",S44,""),IF(AND(O44&lt;&gt;"",Q44=""),O44,IF(AND(O44="",Q44&lt;&gt;""),Q44,IF(ABS(P44-1)&lt;=ABS(13-R44),O44,Q44))))</f>
         <v>0</v>
       </c>
-      <c r="X44" s="8" t="n">
+      <c r="X44" s="1" t="n">
         <f aca="false">IF(OR(V44="",W44=""),"",
   IF(B44="ADD",AND(VALUE(V44)=1,VALUE(W44)=0),
     IF(B44="REMOVE",AND(VALUE(V44)=0,VALUE(W44)=1),
@@ -7561,64 +7569,64 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="1" t="n">
         <v>2.13749671208556</v>
       </c>
-      <c r="F45" s="0" t="n">
+      <c r="F45" s="1" t="n">
         <v>41.3837465996295</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="G45" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H45" s="2" t="str">
+      <c r="H45" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3837465996295,2.13749671208556","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N45" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P45" s="7" t="s">
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P45" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q45" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="V45" s="0" t="str">
+      <c r="Q45" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R45" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S45" s="8"/>
+      <c r="T45" s="8"/>
+      <c r="V45" s="1" t="str">
         <f aca="false">IF(AND(I45="",K45=""),IF(M45&lt;&gt;"",M45,""),IF(AND(I45&lt;&gt;"",K45=""),I45,IF(AND(I45="",K45&lt;&gt;""),K45,IF(ABS(J45-1)&lt;=ABS(13-L45),I45,K45))))</f>
         <v>0</v>
       </c>
-      <c r="W45" s="0" t="str">
+      <c r="W45" s="1" t="str">
         <f aca="false">IF(AND(O45="",Q45=""),IF(S45&lt;&gt;"",S45,""),IF(AND(O45&lt;&gt;"",Q45=""),O45,IF(AND(O45="",Q45&lt;&gt;""),Q45,IF(ABS(P45-1)&lt;=ABS(13-R45),O45,Q45))))</f>
         <v>0</v>
       </c>
-      <c r="X45" s="8" t="n">
+      <c r="X45" s="1" t="n">
         <f aca="false">IF(OR(V45="",W45=""),"",
   IF(B45="ADD",AND(VALUE(V45)=1,VALUE(W45)=0),
     IF(B45="REMOVE",AND(VALUE(V45)=0,VALUE(W45)=1),
@@ -7630,68 +7638,68 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="1" t="n">
         <v>2.18877627141089</v>
       </c>
-      <c r="F46" s="0" t="n">
+      <c r="F46" s="1" t="n">
         <v>41.4180150021324</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H46" s="2" t="str">
+      <c r="H46" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4180150021324,2.18877627141089","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" s="7" t="s">
+      <c r="I46" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L46" s="7" t="s">
+      <c r="K46" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P46" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R46" s="7" t="s">
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P46" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q46" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R46" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="V46" s="0" t="str">
+      <c r="S46" s="8"/>
+      <c r="T46" s="8"/>
+      <c r="V46" s="1" t="str">
         <f aca="false">IF(AND(I46="",K46=""),IF(M46&lt;&gt;"",M46,""),IF(AND(I46&lt;&gt;"",K46=""),I46,IF(AND(I46="",K46&lt;&gt;""),K46,IF(ABS(J46-1)&lt;=ABS(13-L46),I46,K46))))</f>
         <v>0</v>
       </c>
-      <c r="W46" s="0" t="str">
+      <c r="W46" s="1" t="str">
         <f aca="false">IF(AND(O46="",Q46=""),IF(S46&lt;&gt;"",S46,""),IF(AND(O46&lt;&gt;"",Q46=""),O46,IF(AND(O46="",Q46&lt;&gt;""),Q46,IF(ABS(P46-1)&lt;=ABS(13-R46),O46,Q46))))</f>
         <v>0</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="1" t="n">
         <f aca="false">IF(OR(V46="",W46=""),"",
   IF(B46="ADD",AND(VALUE(V46)=1,VALUE(W46)=0),
     IF(B46="REMOVE",AND(VALUE(V46)=0,VALUE(W46)=1),
@@ -7703,60 +7711,60 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="1" t="n">
         <v>2.18231027257586</v>
       </c>
-      <c r="F47" s="0" t="n">
+      <c r="F47" s="1" t="n">
         <v>41.4151958654109</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="H47" s="2" t="str">
+      <c r="H47" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4151958654109,2.18231027257586","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L47" s="7" t="s">
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R47" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="V47" s="0" t="str">
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S47" s="8"/>
+      <c r="T47" s="8"/>
+      <c r="V47" s="1" t="str">
         <f aca="false">IF(AND(I47="",K47=""),IF(M47&lt;&gt;"",M47,""),IF(AND(I47&lt;&gt;"",K47=""),I47,IF(AND(I47="",K47&lt;&gt;""),K47,IF(ABS(J47-1)&lt;=ABS(13-L47),I47,K47))))</f>
         <v>0</v>
       </c>
-      <c r="W47" s="0" t="str">
+      <c r="W47" s="1" t="str">
         <f aca="false">IF(AND(O47="",Q47=""),IF(S47&lt;&gt;"",S47,""),IF(AND(O47&lt;&gt;"",Q47=""),O47,IF(AND(O47="",Q47&lt;&gt;""),Q47,IF(ABS(P47-1)&lt;=ABS(13-R47),O47,Q47))))</f>
         <v>0</v>
       </c>
-      <c r="X47" s="8" t="n">
+      <c r="X47" s="1" t="n">
         <f aca="false">IF(OR(V47="",W47=""),"",
   IF(B47="ADD",AND(VALUE(V47)=1,VALUE(W47)=0),
     IF(B47="REMOVE",AND(VALUE(V47)=0,VALUE(W47)=1),
@@ -7768,64 +7776,64 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="1" t="n">
         <v>2.14940742253693</v>
       </c>
-      <c r="F48" s="0" t="n">
+      <c r="F48" s="1" t="n">
         <v>41.3829948804712</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H48" s="2" t="str">
+      <c r="H48" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3829948804712,2.14940742253693","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L48" s="7" t="s">
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L48" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P48" s="7" t="s">
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P48" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q48" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R48" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="V48" s="0" t="str">
+      <c r="Q48" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R48" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S48" s="8"/>
+      <c r="T48" s="8"/>
+      <c r="V48" s="1" t="str">
         <f aca="false">IF(AND(I48="",K48=""),IF(M48&lt;&gt;"",M48,""),IF(AND(I48&lt;&gt;"",K48=""),I48,IF(AND(I48="",K48&lt;&gt;""),K48,IF(ABS(J48-1)&lt;=ABS(13-L48),I48,K48))))</f>
         <v>0</v>
       </c>
-      <c r="W48" s="0" t="str">
+      <c r="W48" s="1" t="str">
         <f aca="false">IF(AND(O48="",Q48=""),IF(S48&lt;&gt;"",S48,""),IF(AND(O48&lt;&gt;"",Q48=""),O48,IF(AND(O48="",Q48&lt;&gt;""),Q48,IF(ABS(P48-1)&lt;=ABS(13-R48),O48,Q48))))</f>
         <v>0</v>
       </c>
-      <c r="X48" s="8" t="n">
+      <c r="X48" s="1" t="n">
         <f aca="false">IF(OR(V48="",W48=""),"",
   IF(B48="ADD",AND(VALUE(V48)=1,VALUE(W48)=0),
     IF(B48="REMOVE",AND(VALUE(V48)=0,VALUE(W48)=1),
@@ -7837,64 +7845,64 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="1" t="n">
         <v>2.15347263795814</v>
       </c>
-      <c r="F49" s="0" t="n">
+      <c r="F49" s="1" t="n">
         <v>41.3774580559654</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="H49" s="2" t="str">
+      <c r="H49" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3774580559654,2.15347263795814","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L49" s="7" t="s">
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L49" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P49" s="7" t="s">
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P49" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Q49" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R49" s="7" t="s">
+      <c r="Q49" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R49" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="V49" s="0" t="str">
+      <c r="S49" s="8"/>
+      <c r="T49" s="8"/>
+      <c r="V49" s="1" t="str">
         <f aca="false">IF(AND(I49="",K49=""),IF(M49&lt;&gt;"",M49,""),IF(AND(I49&lt;&gt;"",K49=""),I49,IF(AND(I49="",K49&lt;&gt;""),K49,IF(ABS(J49-1)&lt;=ABS(13-L49),I49,K49))))</f>
         <v>0</v>
       </c>
-      <c r="W49" s="0" t="str">
+      <c r="W49" s="1" t="str">
         <f aca="false">IF(AND(O49="",Q49=""),IF(S49&lt;&gt;"",S49,""),IF(AND(O49&lt;&gt;"",Q49=""),O49,IF(AND(O49="",Q49&lt;&gt;""),Q49,IF(ABS(P49-1)&lt;=ABS(13-R49),O49,Q49))))</f>
         <v>0</v>
       </c>
-      <c r="X49" s="8" t="n">
+      <c r="X49" s="1" t="n">
         <f aca="false">IF(OR(V49="",W49=""),"",
   IF(B49="ADD",AND(VALUE(V49)=1,VALUE(W49)=0),
     IF(B49="REMOVE",AND(VALUE(V49)=0,VALUE(W49)=1),
@@ -7906,60 +7914,60 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="1" t="n">
         <v>2.1482642373602</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="1" t="n">
         <v>41.3828585874194</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="G50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H50" s="2" t="str">
+      <c r="H50" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828585874194,2.1482642373602","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N50" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="V50" s="0" t="str">
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R50" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S50" s="8"/>
+      <c r="T50" s="8"/>
+      <c r="V50" s="1" t="str">
         <f aca="false">IF(AND(I50="",K50=""),IF(M50&lt;&gt;"",M50,""),IF(AND(I50&lt;&gt;"",K50=""),I50,IF(AND(I50="",K50&lt;&gt;""),K50,IF(ABS(J50-1)&lt;=ABS(13-L50),I50,K50))))</f>
         <v>0</v>
       </c>
-      <c r="W50" s="0" t="str">
+      <c r="W50" s="1" t="str">
         <f aca="false">IF(AND(O50="",Q50=""),IF(S50&lt;&gt;"",S50,""),IF(AND(O50&lt;&gt;"",Q50=""),O50,IF(AND(O50="",Q50&lt;&gt;""),Q50,IF(ABS(P50-1)&lt;=ABS(13-R50),O50,Q50))))</f>
         <v>0</v>
       </c>
-      <c r="X50" s="8" t="n">
+      <c r="X50" s="1" t="n">
         <f aca="false">IF(OR(V50="",W50=""),"",
   IF(B50="ADD",AND(VALUE(V50)=1,VALUE(W50)=0),
     IF(B50="REMOVE",AND(VALUE(V50)=0,VALUE(W50)=1),
@@ -7971,63 +7979,63 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="1" t="n">
         <v>2.18912239496258</v>
       </c>
-      <c r="F51" s="0" t="n">
+      <c r="F51" s="1" t="n">
         <v>41.3777345900509</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H51" s="2" t="str">
+      <c r="H51" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3777345900509,2.18912239496258","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L51" s="7" t="s">
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L51" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R51" s="7" t="s">
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R51" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="6" t="s">
+      <c r="S51" s="8"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="V51" s="0" t="str">
+      <c r="V51" s="1" t="str">
         <f aca="false">IF(AND(I51="",K51=""),IF(M51&lt;&gt;"",M51,""),IF(AND(I51&lt;&gt;"",K51=""),I51,IF(AND(I51="",K51&lt;&gt;""),K51,IF(ABS(J51-1)&lt;=ABS(13-L51),I51,K51))))</f>
         <v>0</v>
       </c>
-      <c r="W51" s="0" t="str">
+      <c r="W51" s="1" t="str">
         <f aca="false">IF(AND(O51="",Q51=""),IF(S51&lt;&gt;"",S51,""),IF(AND(O51&lt;&gt;"",Q51=""),O51,IF(AND(O51="",Q51&lt;&gt;""),Q51,IF(ABS(P51-1)&lt;=ABS(13-R51),O51,Q51))))</f>
         <v>0</v>
       </c>
-      <c r="X51" s="8" t="n">
+      <c r="X51" s="1" t="n">
         <f aca="false">IF(OR(V51="",W51=""),"",
   IF(B51="ADD",AND(VALUE(V51)=1,VALUE(W51)=0),
     IF(B51="REMOVE",AND(VALUE(V51)=0,VALUE(W51)=1),
@@ -8039,64 +8047,64 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="1" t="n">
         <v>2.1592791307784</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="1" t="n">
         <v>41.3799261629063</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="H52" s="2" t="str">
+      <c r="H52" s="3" t="str">
         <f aca="false">HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3799261629063,2.1592791307784","Open GSV")</f>
         <v>Open GSV</v>
       </c>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L52" s="7" t="s">
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L52" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P52" s="7" t="s">
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P52" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Q52" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R52" s="7" t="s">
+      <c r="Q52" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R52" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="V52" s="0" t="str">
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
+      <c r="V52" s="1" t="str">
         <f aca="false">IF(AND(I52="",K52=""),IF(M52&lt;&gt;"",M52,""),IF(AND(I52&lt;&gt;"",K52=""),I52,IF(AND(I52="",K52&lt;&gt;""),K52,IF(ABS(J52-1)&lt;=ABS(13-L52),I52,K52))))</f>
         <v>0</v>
       </c>
-      <c r="W52" s="0" t="str">
+      <c r="W52" s="1" t="str">
         <f aca="false">IF(AND(O52="",Q52=""),IF(S52&lt;&gt;"",S52,""),IF(AND(O52&lt;&gt;"",Q52=""),O52,IF(AND(O52="",Q52&lt;&gt;""),Q52,IF(ABS(P52-1)&lt;=ABS(13-R52),O52,Q52))))</f>
         <v>0</v>
       </c>
-      <c r="X52" s="8" t="n">
+      <c r="X52" s="1" t="n">
         <f aca="false">IF(OR(V52="",W52=""),"",
   IF(B52="ADD",AND(VALUE(V52)=1,VALUE(W52)=0),
     IF(B52="REMOVE",AND(VALUE(V52)=0,VALUE(W52)=1),
@@ -8128,21 +8136,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
